--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -5421,7 +5421,7 @@
         <v>119010401</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>57384</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>119010404</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>57384</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6027,6 +6027,4742 @@
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128278178</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91926</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>760</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>547794</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6960147</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128278960</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>547724</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6960039</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128278898</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>547758</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6960041</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128279532</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Norrkrången, Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>547624</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6960008</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128278869</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>547767</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6960048</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128284865</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98491</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>547591</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6960277</v>
+      </c>
+      <c r="S57" t="n">
+        <v>4</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128279511</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Norrkrången, Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>547618</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6960012</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128279150</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Norrkrången, Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>547640</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6960059</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128277912</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80133</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>547803</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6960143</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128284869</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>547620</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6960293</v>
+      </c>
+      <c r="S61" t="n">
+        <v>4</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128279022</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>547715</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6960022</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128284859</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>547891</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6960165</v>
+      </c>
+      <c r="S63" t="n">
+        <v>3</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128284872</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>547627</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6960292</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128284868</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>547611</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6960291</v>
+      </c>
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128279803</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92636</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>547600</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6960084</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128280133</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>547601</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6960267</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128280081</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>547586</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6960259</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128278944</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Norrkrången, Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>547605</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6960074</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128284861</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>547812</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6960137</v>
+      </c>
+      <c r="S70" t="n">
+        <v>4</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128284870</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92049</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>547621</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6960289</v>
+      </c>
+      <c r="S71" t="n">
+        <v>4</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128278487</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>547771</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6960077</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128279241</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Norrkrången, Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>547618</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6960049</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128279186</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>547558</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6960050</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128278988</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>547739</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6960028</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128284864</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>547576</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6960160</v>
+      </c>
+      <c r="S76" t="n">
+        <v>4</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>par</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128284860</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92660</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>547847</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6960134</v>
+      </c>
+      <c r="S77" t="n">
+        <v>4</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128278595</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>547811</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6960055</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128278726</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>547806</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6960028</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128284867</v>
+      </c>
+      <c r="B80" t="n">
+        <v>80161</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>547611</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6960292</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128284866</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>547611</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6960291</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128280541</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91926</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>760</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>547656</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6960341</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128277499</v>
+      </c>
+      <c r="B83" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>547884</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6960163</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128277635</v>
+      </c>
+      <c r="B84" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>547856</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6960149</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128279138</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>547548</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6960061</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128277916</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>547828</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6960135</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack på två tallar</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128278608</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>547814</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6960059</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128278910</v>
+      </c>
+      <c r="B88" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>547750</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6960045</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128279883</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>547596</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6960103</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128284862</v>
+      </c>
+      <c r="B90" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>547776</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6960134</v>
+      </c>
+      <c r="S90" t="n">
+        <v>4</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>på gran</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128279069</v>
+      </c>
+      <c r="B91" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Norrkrången, Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>547670</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6960031</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128279287</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91648</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>658</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Norrkrången, Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>547607</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6960041</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128284863</v>
+      </c>
+      <c r="B93" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>547756</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6960112</v>
+      </c>
+      <c r="S93" t="n">
+        <v>4</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128279518</v>
+      </c>
+      <c r="B94" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Norrkrången, Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>547625</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6960017</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128280491</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>547648</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6960333</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6126,49 +6126,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128278960</v>
+        <v>128279532</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547724</v>
+        <v>547624</v>
       </c>
       <c r="R53" t="n">
-        <v>6960039</v>
+        <v>6960008</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6200,7 +6201,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6210,7 +6211,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6225,12 +6231,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6344,50 +6350,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128279532</v>
+        <v>128278960</v>
       </c>
       <c r="B55" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547624</v>
+        <v>547724</v>
       </c>
       <c r="R55" t="n">
-        <v>6960008</v>
+        <v>6960039</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6419,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6429,12 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6449,12 +6449,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6684,54 +6684,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128279511</v>
+        <v>128279150</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>92634</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547618</v>
+        <v>547640</v>
       </c>
       <c r="R58" t="n">
-        <v>6960012</v>
+        <v>6960059</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6763,7 +6754,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6773,7 +6764,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6788,57 +6779,66 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128279150</v>
+        <v>128279511</v>
       </c>
       <c r="B59" t="n">
-        <v>92634</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547640</v>
+        <v>547618</v>
       </c>
       <c r="R59" t="n">
-        <v>6960059</v>
+        <v>6960012</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6895,12 +6895,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7111,48 +7111,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128279022</v>
+        <v>128284859</v>
       </c>
       <c r="B62" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547715</v>
+        <v>547891</v>
       </c>
       <c r="R62" t="n">
-        <v>6960022</v>
+        <v>6960165</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7206,60 +7206,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128284859</v>
+        <v>128279022</v>
       </c>
       <c r="B63" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547891</v>
+        <v>547715</v>
       </c>
       <c r="R63" t="n">
-        <v>6960165</v>
+        <v>6960022</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7313,19 +7313,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B64" t="n">
         <v>98470</v>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R64" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,7 +7432,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B65" t="n">
         <v>98470</v>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R65" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7539,10 +7539,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128279803</v>
+        <v>128280133</v>
       </c>
       <c r="B66" t="n">
-        <v>92636</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7550,34 +7550,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547600</v>
+        <v>547601</v>
       </c>
       <c r="R66" t="n">
-        <v>6960084</v>
+        <v>6960267</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7610,6 +7615,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7636,10 +7646,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128280133</v>
+        <v>128279803</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>92636</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7647,39 +7657,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547601</v>
+        <v>547600</v>
       </c>
       <c r="R67" t="n">
-        <v>6960267</v>
+        <v>6960084</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7712,11 +7717,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7850,52 +7850,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128278944</v>
+        <v>128284861</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547605</v>
+        <v>547812</v>
       </c>
       <c r="R69" t="n">
-        <v>6960074</v>
+        <v>6960137</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7924,7 +7920,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7934,7 +7930,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7949,60 +7945,64 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128284861</v>
+        <v>128278944</v>
       </c>
       <c r="B70" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547812</v>
+        <v>547605</v>
       </c>
       <c r="R70" t="n">
-        <v>6960137</v>
+        <v>6960074</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8056,60 +8056,65 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128284870</v>
+        <v>128278487</v>
       </c>
       <c r="B71" t="n">
-        <v>92049</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547621</v>
+        <v>547771</v>
       </c>
       <c r="R71" t="n">
-        <v>6960289</v>
+        <v>6960077</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8136,19 +8141,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,65 +8163,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128278487</v>
+        <v>128284870</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547771</v>
+        <v>547621</v>
       </c>
       <c r="R72" t="n">
-        <v>6960077</v>
+        <v>6960289</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8248,14 +8243,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8270,12 +8270,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8717,48 +8717,52 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128284860</v>
+        <v>128278726</v>
       </c>
       <c r="B77" t="n">
-        <v>92660</v>
+        <v>98470</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547847</v>
+        <v>547806</v>
       </c>
       <c r="R77" t="n">
-        <v>6960134</v>
+        <v>6960028</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8787,7 +8791,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8797,7 +8801,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,12 +8816,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8931,52 +8935,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278726</v>
+        <v>128284860</v>
       </c>
       <c r="B79" t="n">
-        <v>98470</v>
+        <v>92660</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547806</v>
+        <v>547847</v>
       </c>
       <c r="R79" t="n">
-        <v>6960028</v>
+        <v>6960134</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,44 +9030,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128284867</v>
+        <v>128280541</v>
       </c>
       <c r="B80" t="n">
-        <v>80161</v>
+        <v>91926</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9077,13 +9077,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R80" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9110,19 +9110,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9137,19 +9127,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128284866</v>
+        <v>128277499</v>
       </c>
       <c r="B81" t="n">
         <v>80132</v>
@@ -9180,14 +9170,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>547611</v>
+        <v>547884</v>
       </c>
       <c r="R81" t="n">
-        <v>6960291</v>
+        <v>6960163</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9219,7 +9209,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9229,7 +9219,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9244,44 +9234,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128280541</v>
+        <v>128284867</v>
       </c>
       <c r="B82" t="n">
-        <v>91926</v>
+        <v>80161</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9291,13 +9281,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R82" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9324,9 +9314,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9341,19 +9341,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128277499</v>
+        <v>128284866</v>
       </c>
       <c r="B83" t="n">
         <v>80132</v>
@@ -9384,14 +9384,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>547884</v>
+        <v>547611</v>
       </c>
       <c r="R83" t="n">
-        <v>6960163</v>
+        <v>6960291</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9448,12 +9448,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9791,52 +9791,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128278608</v>
+        <v>128284862</v>
       </c>
       <c r="B87" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>547814</v>
+        <v>547776</v>
       </c>
       <c r="R87" t="n">
-        <v>6960059</v>
+        <v>6960134</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9865,7 +9861,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9875,7 +9871,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9890,12 +9891,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10013,7 +10014,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128279883</v>
+        <v>128278608</v>
       </c>
       <c r="B89" t="n">
         <v>98470</v>
@@ -10043,19 +10044,19 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>547596</v>
+        <v>547814</v>
       </c>
       <c r="R89" t="n">
-        <v>6960103</v>
+        <v>6960059</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10085,9 +10086,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10102,60 +10113,64 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128284862</v>
+        <v>128279883</v>
       </c>
       <c r="B90" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>547776</v>
+        <v>547596</v>
       </c>
       <c r="R90" t="n">
-        <v>6960134</v>
+        <v>6960103</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10182,24 +10197,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10214,12 +10214,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10333,10 +10333,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128279287</v>
+        <v>128284863</v>
       </c>
       <c r="B92" t="n">
-        <v>91648</v>
+        <v>56855</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10344,37 +10344,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>547607</v>
+        <v>547756</v>
       </c>
       <c r="R92" t="n">
-        <v>6960041</v>
+        <v>6960112</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10428,22 +10428,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128284863</v>
+        <v>128279287</v>
       </c>
       <c r="B93" t="n">
-        <v>56855</v>
+        <v>91648</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,37 +10451,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547756</v>
+        <v>547607</v>
       </c>
       <c r="R93" t="n">
-        <v>6960112</v>
+        <v>6960041</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,12 +10535,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10763,6 +10763,122 @@
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128278124</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>547798</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6960102</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6350,52 +6350,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128278960</v>
+        <v>128284865</v>
       </c>
       <c r="B55" t="n">
-        <v>98470</v>
+        <v>98491</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547724</v>
+        <v>547591</v>
       </c>
       <c r="R55" t="n">
-        <v>6960039</v>
+        <v>6960277</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6424,7 +6420,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6430,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6449,19 +6445,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128278869</v>
+        <v>128278960</v>
       </c>
       <c r="B56" t="n">
         <v>98470</v>
@@ -6491,12 +6487,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6505,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547767</v>
+        <v>547724</v>
       </c>
       <c r="R56" t="n">
-        <v>6960048</v>
+        <v>6960039</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6540,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6550,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6565,60 +6556,69 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128284865</v>
+        <v>128278869</v>
       </c>
       <c r="B57" t="n">
-        <v>98491</v>
+        <v>98470</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547591</v>
+        <v>547767</v>
       </c>
       <c r="R57" t="n">
-        <v>6960277</v>
+        <v>6960048</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,12 +6672,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7111,48 +7111,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128284859</v>
+        <v>128279022</v>
       </c>
       <c r="B62" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547891</v>
+        <v>547715</v>
       </c>
       <c r="R62" t="n">
-        <v>6960165</v>
+        <v>6960022</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7206,60 +7206,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128279022</v>
+        <v>128284859</v>
       </c>
       <c r="B63" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547715</v>
+        <v>547891</v>
       </c>
       <c r="R63" t="n">
-        <v>6960022</v>
+        <v>6960165</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7313,12 +7313,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8494,52 +8494,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B75" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R75" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8568,7 +8564,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8578,7 +8574,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8593,60 +8594,64 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B76" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R76" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8675,7 +8680,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8685,12 +8690,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,12 +8705,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9460,45 +9460,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128277635</v>
+        <v>128279138</v>
       </c>
       <c r="B84" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>547856</v>
+        <v>547548</v>
       </c>
       <c r="R84" t="n">
-        <v>6960149</v>
+        <v>6960061</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,19 +9533,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9555,62 +9555,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128279138</v>
+        <v>128277635</v>
       </c>
       <c r="B85" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>547548</v>
+        <v>547856</v>
       </c>
       <c r="R85" t="n">
-        <v>6960061</v>
+        <v>6960149</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9640,14 +9635,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9662,12 +9662,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -7111,48 +7111,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128279022</v>
+        <v>128284859</v>
       </c>
       <c r="B62" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547715</v>
+        <v>547891</v>
       </c>
       <c r="R62" t="n">
-        <v>6960022</v>
+        <v>6960165</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7206,60 +7206,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128284859</v>
+        <v>128279022</v>
       </c>
       <c r="B63" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547891</v>
+        <v>547715</v>
       </c>
       <c r="R63" t="n">
-        <v>6960165</v>
+        <v>6960022</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7313,12 +7313,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8068,53 +8068,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128278487</v>
+        <v>128284870</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547771</v>
+        <v>547621</v>
       </c>
       <c r="R71" t="n">
-        <v>6960077</v>
+        <v>6960289</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8141,14 +8136,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,60 +8163,65 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128284870</v>
+        <v>128278487</v>
       </c>
       <c r="B72" t="n">
-        <v>92049</v>
+        <v>57672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547621</v>
+        <v>547771</v>
       </c>
       <c r="R72" t="n">
-        <v>6960289</v>
+        <v>6960077</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8243,19 +8248,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8270,12 +8270,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8717,49 +8717,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128278726</v>
+        <v>128278595</v>
       </c>
       <c r="B77" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547806</v>
+        <v>547811</v>
       </c>
       <c r="R77" t="n">
-        <v>6960028</v>
+        <v>6960055</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8791,7 +8787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8801,7 +8797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,22 +8812,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128278595</v>
+        <v>128284860</v>
       </c>
       <c r="B78" t="n">
-        <v>80132</v>
+        <v>92660</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8839,37 +8835,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>4368</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547811</v>
+        <v>547847</v>
       </c>
       <c r="R78" t="n">
-        <v>6960055</v>
+        <v>6960134</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8898,7 +8894,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8908,7 +8904,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8923,60 +8919,64 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128284860</v>
+        <v>128278726</v>
       </c>
       <c r="B79" t="n">
-        <v>92660</v>
+        <v>98470</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547847</v>
+        <v>547806</v>
       </c>
       <c r="R79" t="n">
-        <v>6960134</v>
+        <v>6960028</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,12 +9030,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10226,10 +10226,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128279069</v>
+        <v>128279287</v>
       </c>
       <c r="B91" t="n">
-        <v>80132</v>
+        <v>91648</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,21 +10237,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547670</v>
+        <v>547607</v>
       </c>
       <c r="R91" t="n">
-        <v>6960031</v>
+        <v>6960041</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10333,10 +10333,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128284863</v>
+        <v>128279069</v>
       </c>
       <c r="B92" t="n">
-        <v>56855</v>
+        <v>80132</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10344,37 +10344,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>547756</v>
+        <v>547670</v>
       </c>
       <c r="R92" t="n">
-        <v>6960112</v>
+        <v>6960031</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10428,22 +10428,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128279287</v>
+        <v>128284863</v>
       </c>
       <c r="B93" t="n">
-        <v>91648</v>
+        <v>56855</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,37 +10451,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547607</v>
+        <v>547756</v>
       </c>
       <c r="R93" t="n">
-        <v>6960041</v>
+        <v>6960112</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,12 +10535,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6350,48 +6350,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128284865</v>
+        <v>128278960</v>
       </c>
       <c r="B55" t="n">
-        <v>98491</v>
+        <v>98470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547591</v>
+        <v>547724</v>
       </c>
       <c r="R55" t="n">
-        <v>6960277</v>
+        <v>6960039</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6420,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6430,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6445,19 +6449,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128278960</v>
+        <v>128278869</v>
       </c>
       <c r="B56" t="n">
         <v>98470</v>
@@ -6487,7 +6491,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6496,10 +6505,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547724</v>
+        <v>547767</v>
       </c>
       <c r="R56" t="n">
-        <v>6960039</v>
+        <v>6960048</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6540,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6550,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6556,69 +6565,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128278869</v>
+        <v>128284865</v>
       </c>
       <c r="B57" t="n">
-        <v>98470</v>
+        <v>98491</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547767</v>
+        <v>547591</v>
       </c>
       <c r="R57" t="n">
-        <v>6960048</v>
+        <v>6960277</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,57 +6672,66 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128279150</v>
+        <v>128279511</v>
       </c>
       <c r="B58" t="n">
-        <v>92634</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547640</v>
+        <v>547618</v>
       </c>
       <c r="R58" t="n">
-        <v>6960059</v>
+        <v>6960012</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6754,7 +6763,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6764,7 +6773,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6779,66 +6788,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128279511</v>
+        <v>128279150</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>92634</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547618</v>
+        <v>547640</v>
       </c>
       <c r="R59" t="n">
-        <v>6960012</v>
+        <v>6960059</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6895,12 +6895,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7111,48 +7111,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128284859</v>
+        <v>128279022</v>
       </c>
       <c r="B62" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547891</v>
+        <v>547715</v>
       </c>
       <c r="R62" t="n">
-        <v>6960165</v>
+        <v>6960022</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7206,60 +7206,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128279022</v>
+        <v>128284859</v>
       </c>
       <c r="B63" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547715</v>
+        <v>547891</v>
       </c>
       <c r="R63" t="n">
-        <v>6960022</v>
+        <v>6960165</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7313,12 +7313,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128280133</v>
+        <v>128279803</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>92636</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7550,39 +7550,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547601</v>
+        <v>547600</v>
       </c>
       <c r="R66" t="n">
-        <v>6960267</v>
+        <v>6960084</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7615,11 +7610,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7646,10 +7636,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128279803</v>
+        <v>128280133</v>
       </c>
       <c r="B67" t="n">
-        <v>92636</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7657,34 +7647,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547600</v>
+        <v>547601</v>
       </c>
       <c r="R67" t="n">
-        <v>6960084</v>
+        <v>6960267</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7717,6 +7712,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8068,48 +8068,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128284870</v>
+        <v>128278487</v>
       </c>
       <c r="B71" t="n">
-        <v>92049</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547621</v>
+        <v>547771</v>
       </c>
       <c r="R71" t="n">
-        <v>6960289</v>
+        <v>6960077</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8136,19 +8141,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,65 +8163,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128278487</v>
+        <v>128284870</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547771</v>
+        <v>547621</v>
       </c>
       <c r="R72" t="n">
-        <v>6960077</v>
+        <v>6960289</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8248,14 +8243,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8270,12 +8270,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -8068,53 +8068,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128278487</v>
+        <v>128284870</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547771</v>
+        <v>547621</v>
       </c>
       <c r="R71" t="n">
-        <v>6960077</v>
+        <v>6960289</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8141,14 +8136,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,60 +8163,65 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128284870</v>
+        <v>128278487</v>
       </c>
       <c r="B72" t="n">
-        <v>92049</v>
+        <v>57672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547621</v>
+        <v>547771</v>
       </c>
       <c r="R72" t="n">
-        <v>6960289</v>
+        <v>6960077</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8243,19 +8248,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8270,12 +8270,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8494,48 +8494,52 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B75" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R75" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8564,7 +8568,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8574,12 +8578,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8594,64 +8593,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B76" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R76" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8680,7 +8675,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8690,7 +8685,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,12 +8705,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9460,50 +9460,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128279138</v>
+        <v>128277635</v>
       </c>
       <c r="B84" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>547548</v>
+        <v>547856</v>
       </c>
       <c r="R84" t="n">
-        <v>6960061</v>
+        <v>6960149</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9533,14 +9528,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9555,57 +9555,62 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128277635</v>
+        <v>128279138</v>
       </c>
       <c r="B85" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>547856</v>
+        <v>547548</v>
       </c>
       <c r="R85" t="n">
-        <v>6960149</v>
+        <v>6960061</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,19 +9640,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9662,12 +9662,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6350,52 +6350,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128278960</v>
+        <v>128284865</v>
       </c>
       <c r="B55" t="n">
-        <v>98470</v>
+        <v>98491</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547724</v>
+        <v>547591</v>
       </c>
       <c r="R55" t="n">
-        <v>6960039</v>
+        <v>6960277</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6424,7 +6420,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6430,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6449,19 +6445,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128278869</v>
+        <v>128278960</v>
       </c>
       <c r="B56" t="n">
         <v>98470</v>
@@ -6491,12 +6487,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6505,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547767</v>
+        <v>547724</v>
       </c>
       <c r="R56" t="n">
-        <v>6960048</v>
+        <v>6960039</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6540,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6550,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6565,60 +6556,69 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128284865</v>
+        <v>128278869</v>
       </c>
       <c r="B57" t="n">
-        <v>98491</v>
+        <v>98470</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547591</v>
+        <v>547767</v>
       </c>
       <c r="R57" t="n">
-        <v>6960277</v>
+        <v>6960048</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,66 +6672,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128279511</v>
+        <v>128279150</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>92634</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547618</v>
+        <v>547640</v>
       </c>
       <c r="R58" t="n">
-        <v>6960012</v>
+        <v>6960059</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6763,7 +6754,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6773,7 +6764,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6788,57 +6779,66 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128279150</v>
+        <v>128279511</v>
       </c>
       <c r="B59" t="n">
-        <v>92634</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547640</v>
+        <v>547618</v>
       </c>
       <c r="R59" t="n">
-        <v>6960059</v>
+        <v>6960012</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6895,12 +6895,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128279803</v>
+        <v>128280133</v>
       </c>
       <c r="B66" t="n">
-        <v>92636</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7550,34 +7550,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547600</v>
+        <v>547601</v>
       </c>
       <c r="R66" t="n">
-        <v>6960084</v>
+        <v>6960267</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7610,6 +7615,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7636,10 +7646,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128280133</v>
+        <v>128279803</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>92636</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7647,39 +7657,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547601</v>
+        <v>547600</v>
       </c>
       <c r="R67" t="n">
-        <v>6960267</v>
+        <v>6960084</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7712,11 +7717,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8494,52 +8494,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B75" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R75" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8568,7 +8564,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8578,7 +8574,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8593,60 +8594,64 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B76" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R76" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8675,7 +8680,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8685,12 +8690,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,57 +8705,61 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128278595</v>
+        <v>128278726</v>
       </c>
       <c r="B77" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547811</v>
+        <v>547806</v>
       </c>
       <c r="R77" t="n">
-        <v>6960055</v>
+        <v>6960028</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8787,7 +8791,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8797,7 +8801,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,22 +8816,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128284860</v>
+        <v>128278595</v>
       </c>
       <c r="B78" t="n">
-        <v>92660</v>
+        <v>80132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8835,37 +8839,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4368</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547847</v>
+        <v>547811</v>
       </c>
       <c r="R78" t="n">
-        <v>6960134</v>
+        <v>6960055</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8894,7 +8898,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8904,7 +8908,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8919,64 +8923,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278726</v>
+        <v>128284860</v>
       </c>
       <c r="B79" t="n">
-        <v>98470</v>
+        <v>92660</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547806</v>
+        <v>547847</v>
       </c>
       <c r="R79" t="n">
-        <v>6960028</v>
+        <v>6960134</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,12 +9030,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9460,45 +9460,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128277635</v>
+        <v>128279138</v>
       </c>
       <c r="B84" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>547856</v>
+        <v>547548</v>
       </c>
       <c r="R84" t="n">
-        <v>6960149</v>
+        <v>6960061</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,19 +9533,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9555,62 +9555,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128279138</v>
+        <v>128277635</v>
       </c>
       <c r="B85" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>547548</v>
+        <v>547856</v>
       </c>
       <c r="R85" t="n">
-        <v>6960061</v>
+        <v>6960149</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9640,14 +9635,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9662,12 +9662,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10226,10 +10226,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128279287</v>
+        <v>128279069</v>
       </c>
       <c r="B91" t="n">
-        <v>91648</v>
+        <v>80132</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,21 +10237,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547607</v>
+        <v>547670</v>
       </c>
       <c r="R91" t="n">
-        <v>6960041</v>
+        <v>6960031</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10333,10 +10333,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128279069</v>
+        <v>128284863</v>
       </c>
       <c r="B92" t="n">
-        <v>80132</v>
+        <v>56855</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10344,37 +10344,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>547670</v>
+        <v>547756</v>
       </c>
       <c r="R92" t="n">
-        <v>6960031</v>
+        <v>6960112</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10428,22 +10428,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128284863</v>
+        <v>128279287</v>
       </c>
       <c r="B93" t="n">
-        <v>56855</v>
+        <v>91648</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,37 +10451,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547756</v>
+        <v>547607</v>
       </c>
       <c r="R93" t="n">
-        <v>6960112</v>
+        <v>6960041</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,12 +10535,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6684,45 +6684,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128279150</v>
+        <v>128279511</v>
       </c>
       <c r="B58" t="n">
-        <v>92634</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547640</v>
+        <v>547618</v>
       </c>
       <c r="R58" t="n">
-        <v>6960059</v>
+        <v>6960012</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6754,7 +6763,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6764,7 +6773,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6779,66 +6788,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128279511</v>
+        <v>128279150</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>92634</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547618</v>
+        <v>547640</v>
       </c>
       <c r="R59" t="n">
-        <v>6960012</v>
+        <v>6960059</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6895,12 +6895,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -8068,48 +8068,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128284870</v>
+        <v>128278487</v>
       </c>
       <c r="B71" t="n">
-        <v>92049</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547621</v>
+        <v>547771</v>
       </c>
       <c r="R71" t="n">
-        <v>6960289</v>
+        <v>6960077</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8136,19 +8141,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,65 +8163,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128278487</v>
+        <v>128284870</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547771</v>
+        <v>547621</v>
       </c>
       <c r="R72" t="n">
-        <v>6960077</v>
+        <v>6960289</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8248,14 +8243,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8270,12 +8270,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8494,48 +8494,52 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B75" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R75" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8564,7 +8568,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8574,12 +8578,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8594,64 +8593,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B76" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R76" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8680,7 +8675,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8690,7 +8685,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,61 +8705,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128278726</v>
+        <v>128278595</v>
       </c>
       <c r="B77" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547806</v>
+        <v>547811</v>
       </c>
       <c r="R77" t="n">
-        <v>6960028</v>
+        <v>6960055</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8791,7 +8787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8801,7 +8797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,22 +8812,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128278595</v>
+        <v>128284860</v>
       </c>
       <c r="B78" t="n">
-        <v>80132</v>
+        <v>92660</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8839,37 +8835,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>4368</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547811</v>
+        <v>547847</v>
       </c>
       <c r="R78" t="n">
-        <v>6960055</v>
+        <v>6960134</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8898,7 +8894,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8908,7 +8904,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8923,60 +8919,64 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128284860</v>
+        <v>128278726</v>
       </c>
       <c r="B79" t="n">
-        <v>92660</v>
+        <v>98470</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547847</v>
+        <v>547806</v>
       </c>
       <c r="R79" t="n">
-        <v>6960134</v>
+        <v>6960028</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,12 +9030,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6032,7 +6032,7 @@
         <v>128278178</v>
       </c>
       <c r="B52" t="n">
-        <v>91926</v>
+        <v>91934</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6126,53 +6126,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128279532</v>
+        <v>128284865</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>98499</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547624</v>
+        <v>547591</v>
       </c>
       <c r="R53" t="n">
-        <v>6960008</v>
+        <v>6960277</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6201,7 +6196,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6211,12 +6206,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6231,57 +6221,61 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128278898</v>
+        <v>128278960</v>
       </c>
       <c r="B54" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547758</v>
+        <v>547724</v>
       </c>
       <c r="R54" t="n">
-        <v>6960041</v>
+        <v>6960039</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6313,7 +6307,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6323,7 +6317,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6338,60 +6332,69 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128284865</v>
+        <v>128278869</v>
       </c>
       <c r="B55" t="n">
-        <v>98491</v>
+        <v>98478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547591</v>
+        <v>547767</v>
       </c>
       <c r="R55" t="n">
-        <v>6960277</v>
+        <v>6960048</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6420,7 +6423,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6430,7 +6433,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6445,61 +6448,62 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128278960</v>
+        <v>128279532</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547724</v>
+        <v>547624</v>
       </c>
       <c r="R56" t="n">
-        <v>6960039</v>
+        <v>6960008</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6535,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6545,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6556,66 +6565,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128278869</v>
+        <v>128278898</v>
       </c>
       <c r="B57" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547767</v>
+        <v>547758</v>
       </c>
       <c r="R57" t="n">
-        <v>6960048</v>
+        <v>6960041</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6684,54 +6684,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128279511</v>
+        <v>128279150</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547618</v>
+        <v>547640</v>
       </c>
       <c r="R58" t="n">
-        <v>6960012</v>
+        <v>6960059</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6763,7 +6754,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6773,7 +6764,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6788,57 +6779,66 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128279150</v>
+        <v>128279511</v>
       </c>
       <c r="B59" t="n">
-        <v>92634</v>
+        <v>98478</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547640</v>
+        <v>547618</v>
       </c>
       <c r="R59" t="n">
-        <v>6960059</v>
+        <v>6960012</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6895,12 +6895,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6910,7 +6910,7 @@
         <v>128277912</v>
       </c>
       <c r="B60" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>128284869</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>128279022</v>
       </c>
       <c r="B62" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>128284859</v>
       </c>
       <c r="B63" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7325,10 +7325,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B64" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R64" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,10 +7432,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B65" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R65" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7539,10 +7539,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128280133</v>
+        <v>128279803</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>92644</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7550,39 +7550,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547601</v>
+        <v>547600</v>
       </c>
       <c r="R66" t="n">
-        <v>6960267</v>
+        <v>6960084</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7615,11 +7610,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7646,10 +7636,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128279803</v>
+        <v>128280081</v>
       </c>
       <c r="B67" t="n">
-        <v>92636</v>
+        <v>57673</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7657,34 +7647,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547600</v>
+        <v>547586</v>
       </c>
       <c r="R67" t="n">
-        <v>6960084</v>
+        <v>6960259</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7717,6 +7712,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7743,10 +7743,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B68" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R68" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7853,7 +7853,7 @@
         <v>128284861</v>
       </c>
       <c r="B69" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>128278944</v>
       </c>
       <c r="B70" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>128278487</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,48 +8175,52 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128284870</v>
+        <v>128279241</v>
       </c>
       <c r="B72" t="n">
-        <v>92049</v>
+        <v>98478</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547621</v>
+        <v>547618</v>
       </c>
       <c r="R72" t="n">
-        <v>6960289</v>
+        <v>6960049</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8245,7 +8249,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8255,7 +8259,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8270,22 +8274,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128279241</v>
+        <v>128279186</v>
       </c>
       <c r="B73" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8317,14 +8321,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>547618</v>
+        <v>547558</v>
       </c>
       <c r="R73" t="n">
-        <v>6960049</v>
+        <v>6960050</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8354,19 +8358,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8381,64 +8375,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128279186</v>
+        <v>128284870</v>
       </c>
       <c r="B74" t="n">
-        <v>98470</v>
+        <v>92057</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>547558</v>
+        <v>547621</v>
       </c>
       <c r="R74" t="n">
-        <v>6960050</v>
+        <v>6960289</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8465,9 +8455,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8482,64 +8482,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B75" t="n">
-        <v>98470</v>
+        <v>57833</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R75" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8568,7 +8564,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8578,7 +8574,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8593,60 +8594,64 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B76" t="n">
-        <v>57832</v>
+        <v>98478</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R76" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8675,7 +8680,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8685,12 +8690,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,22 +8705,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128278595</v>
+        <v>128284860</v>
       </c>
       <c r="B77" t="n">
-        <v>80132</v>
+        <v>92668</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8728,37 +8728,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>4368</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547811</v>
+        <v>547847</v>
       </c>
       <c r="R77" t="n">
-        <v>6960055</v>
+        <v>6960134</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,22 +8812,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128284860</v>
+        <v>128278595</v>
       </c>
       <c r="B78" t="n">
-        <v>92660</v>
+        <v>80135</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8835,37 +8835,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4368</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547847</v>
+        <v>547811</v>
       </c>
       <c r="R78" t="n">
-        <v>6960134</v>
+        <v>6960055</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8919,12 +8919,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8934,7 +8934,7 @@
         <v>128278726</v>
       </c>
       <c r="B79" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>128280541</v>
       </c>
       <c r="B80" t="n">
-        <v>91926</v>
+        <v>91934</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>128277499</v>
       </c>
       <c r="B81" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>128284867</v>
       </c>
       <c r="B82" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>128284866</v>
       </c>
       <c r="B83" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9460,50 +9460,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128279138</v>
+        <v>128277635</v>
       </c>
       <c r="B84" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>547548</v>
+        <v>547856</v>
       </c>
       <c r="R84" t="n">
-        <v>6960061</v>
+        <v>6960149</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9533,14 +9528,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9555,57 +9555,62 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128277635</v>
+        <v>128279138</v>
       </c>
       <c r="B85" t="n">
-        <v>92642</v>
+        <v>57673</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>547856</v>
+        <v>547548</v>
       </c>
       <c r="R85" t="n">
-        <v>6960149</v>
+        <v>6960061</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,19 +9640,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9662,12 +9662,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9677,7 +9677,7 @@
         <v>128277916</v>
       </c>
       <c r="B86" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9791,48 +9791,52 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128284862</v>
+        <v>128278910</v>
       </c>
       <c r="B87" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>547776</v>
+        <v>547750</v>
       </c>
       <c r="R87" t="n">
-        <v>6960134</v>
+        <v>6960045</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9861,7 +9865,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9871,12 +9875,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9891,22 +9890,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128278910</v>
+        <v>128278608</v>
       </c>
       <c r="B88" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9933,7 +9932,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9942,10 +9941,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>547750</v>
+        <v>547814</v>
       </c>
       <c r="R88" t="n">
-        <v>6960045</v>
+        <v>6960059</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9977,7 +9976,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9987,7 +9986,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10014,10 +10013,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128278608</v>
+        <v>128279883</v>
       </c>
       <c r="B89" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10044,19 +10043,19 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>547814</v>
+        <v>547596</v>
       </c>
       <c r="R89" t="n">
-        <v>6960059</v>
+        <v>6960103</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10086,19 +10085,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10113,64 +10102,60 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128279883</v>
+        <v>128284862</v>
       </c>
       <c r="B90" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>547596</v>
+        <v>547776</v>
       </c>
       <c r="R90" t="n">
-        <v>6960103</v>
+        <v>6960134</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10197,9 +10182,24 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10214,22 +10214,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128279069</v>
+        <v>128279287</v>
       </c>
       <c r="B91" t="n">
-        <v>80132</v>
+        <v>91656</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,21 +10237,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547670</v>
+        <v>547607</v>
       </c>
       <c r="R91" t="n">
-        <v>6960031</v>
+        <v>6960041</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10333,10 +10333,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128284863</v>
+        <v>128279069</v>
       </c>
       <c r="B92" t="n">
-        <v>56855</v>
+        <v>80135</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10344,37 +10344,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>547756</v>
+        <v>547670</v>
       </c>
       <c r="R92" t="n">
-        <v>6960112</v>
+        <v>6960031</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10428,22 +10428,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128279287</v>
+        <v>128284863</v>
       </c>
       <c r="B93" t="n">
-        <v>91648</v>
+        <v>56855</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,37 +10451,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547607</v>
+        <v>547756</v>
       </c>
       <c r="R93" t="n">
-        <v>6960041</v>
+        <v>6960112</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,12 +10535,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
         <v>128279518</v>
       </c>
       <c r="B94" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>128280491</v>
       </c>
       <c r="B95" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>128278124</v>
       </c>
       <c r="B96" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -8068,50 +8068,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128278487</v>
+        <v>128279241</v>
       </c>
       <c r="B71" t="n">
-        <v>57673</v>
+        <v>98478</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547771</v>
+        <v>547618</v>
       </c>
       <c r="R71" t="n">
-        <v>6960077</v>
+        <v>6960049</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8141,14 +8140,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,19 +8167,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128279241</v>
+        <v>128279186</v>
       </c>
       <c r="B72" t="n">
         <v>98478</v>
@@ -8210,14 +8214,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547618</v>
+        <v>547558</v>
       </c>
       <c r="R72" t="n">
-        <v>6960049</v>
+        <v>6960050</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8247,19 +8251,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8274,64 +8268,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128279186</v>
+        <v>128284870</v>
       </c>
       <c r="B73" t="n">
-        <v>98478</v>
+        <v>92057</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>547558</v>
+        <v>547621</v>
       </c>
       <c r="R73" t="n">
-        <v>6960050</v>
+        <v>6960289</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8358,9 +8348,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8375,60 +8375,65 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128284870</v>
+        <v>128278487</v>
       </c>
       <c r="B74" t="n">
-        <v>92057</v>
+        <v>57673</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>547621</v>
+        <v>547771</v>
       </c>
       <c r="R74" t="n">
-        <v>6960289</v>
+        <v>6960077</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8455,19 +8460,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8482,12 +8482,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8824,45 +8824,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128278595</v>
+        <v>128278726</v>
       </c>
       <c r="B78" t="n">
-        <v>80135</v>
+        <v>98478</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547811</v>
+        <v>547806</v>
       </c>
       <c r="R78" t="n">
-        <v>6960055</v>
+        <v>6960028</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8894,7 +8898,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8904,7 +8908,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8919,61 +8923,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278726</v>
+        <v>128278595</v>
       </c>
       <c r="B79" t="n">
-        <v>98478</v>
+        <v>80135</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547806</v>
+        <v>547811</v>
       </c>
       <c r="R79" t="n">
-        <v>6960028</v>
+        <v>6960055</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,57 +9030,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128280541</v>
+        <v>128277499</v>
       </c>
       <c r="B80" t="n">
-        <v>91934</v>
+        <v>80135</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>547656</v>
+        <v>547884</v>
       </c>
       <c r="R80" t="n">
-        <v>6960341</v>
+        <v>6960163</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9110,9 +9110,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9127,60 +9137,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128277499</v>
+        <v>128284867</v>
       </c>
       <c r="B81" t="n">
-        <v>80135</v>
+        <v>80164</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>547884</v>
+        <v>547611</v>
       </c>
       <c r="R81" t="n">
-        <v>6960163</v>
+        <v>6960292</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9209,7 +9219,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9219,7 +9229,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9234,44 +9244,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128284867</v>
+        <v>128284866</v>
       </c>
       <c r="B82" t="n">
-        <v>80164</v>
+        <v>80135</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9284,10 +9294,10 @@
         <v>547611</v>
       </c>
       <c r="R82" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9353,32 +9363,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128284866</v>
+        <v>128280541</v>
       </c>
       <c r="B83" t="n">
-        <v>80135</v>
+        <v>91934</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9388,10 +9398,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R83" t="n">
-        <v>6960291</v>
+        <v>6960341</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,19 +9431,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9448,12 +9448,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6032,7 +6032,7 @@
         <v>128278178</v>
       </c>
       <c r="B52" t="n">
-        <v>91934</v>
+        <v>92026</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6126,48 +6126,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128284865</v>
+        <v>128278898</v>
       </c>
       <c r="B53" t="n">
-        <v>98499</v>
+        <v>80188</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547591</v>
+        <v>547758</v>
       </c>
       <c r="R53" t="n">
-        <v>6960277</v>
+        <v>6960041</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6221,64 +6221,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128278960</v>
+        <v>128284865</v>
       </c>
       <c r="B54" t="n">
-        <v>98478</v>
+        <v>98592</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547724</v>
+        <v>547591</v>
       </c>
       <c r="R54" t="n">
-        <v>6960039</v>
+        <v>6960277</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6307,7 +6303,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6317,7 +6313,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6332,12 +6328,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6347,7 +6343,7 @@
         <v>128278869</v>
       </c>
       <c r="B55" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6460,50 +6456,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128279532</v>
+        <v>128278960</v>
       </c>
       <c r="B56" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547624</v>
+        <v>547724</v>
       </c>
       <c r="R56" t="n">
-        <v>6960008</v>
+        <v>6960039</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6535,7 +6530,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6545,12 +6540,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6565,22 +6555,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128278898</v>
+        <v>128279532</v>
       </c>
       <c r="B57" t="n">
-        <v>80135</v>
+        <v>57685</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6588,34 +6578,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547758</v>
+        <v>547624</v>
       </c>
       <c r="R57" t="n">
-        <v>6960041</v>
+        <v>6960008</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6647,7 +6642,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6652,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6687,7 +6687,7 @@
         <v>128279150</v>
       </c>
       <c r="B58" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>128279511</v>
       </c>
       <c r="B59" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>128277912</v>
       </c>
       <c r="B60" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>128284869</v>
       </c>
       <c r="B61" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>128279022</v>
       </c>
       <c r="B62" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>128284859</v>
       </c>
       <c r="B63" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7325,10 +7325,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B64" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R64" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,10 +7432,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B65" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R65" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7542,7 +7542,7 @@
         <v>128279803</v>
       </c>
       <c r="B66" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>128280081</v>
       </c>
       <c r="B67" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>128280133</v>
       </c>
       <c r="B68" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7850,48 +7850,52 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128284861</v>
+        <v>128278944</v>
       </c>
       <c r="B69" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547812</v>
+        <v>547605</v>
       </c>
       <c r="R69" t="n">
-        <v>6960137</v>
+        <v>6960074</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7920,7 +7924,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7930,7 +7934,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7945,64 +7949,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128278944</v>
+        <v>128284861</v>
       </c>
       <c r="B70" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547605</v>
+        <v>547812</v>
       </c>
       <c r="R70" t="n">
-        <v>6960074</v>
+        <v>6960137</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8056,64 +8056,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128279241</v>
+        <v>128284870</v>
       </c>
       <c r="B71" t="n">
-        <v>98478</v>
+        <v>92149</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547618</v>
+        <v>547621</v>
       </c>
       <c r="R71" t="n">
-        <v>6960049</v>
+        <v>6960289</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8142,7 +8138,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8152,7 +8148,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8167,61 +8163,62 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128279186</v>
+        <v>128278487</v>
       </c>
       <c r="B72" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547558</v>
+        <v>547771</v>
       </c>
       <c r="R72" t="n">
-        <v>6960050</v>
+        <v>6960077</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8254,6 +8251,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8280,48 +8282,52 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128284870</v>
+        <v>128279241</v>
       </c>
       <c r="B73" t="n">
-        <v>92057</v>
+        <v>98571</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>547621</v>
+        <v>547618</v>
       </c>
       <c r="R73" t="n">
-        <v>6960289</v>
+        <v>6960049</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8350,7 +8356,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8360,7 +8366,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8375,62 +8381,61 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128278487</v>
+        <v>128279186</v>
       </c>
       <c r="B74" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>547771</v>
+        <v>547558</v>
       </c>
       <c r="R74" t="n">
-        <v>6960077</v>
+        <v>6960050</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8463,11 +8468,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8494,48 +8494,52 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B75" t="n">
-        <v>57833</v>
+        <v>98571</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R75" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8564,7 +8568,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8574,12 +8578,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8594,64 +8593,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B76" t="n">
-        <v>98478</v>
+        <v>57845</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R76" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8680,7 +8675,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8690,7 +8685,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,22 +8705,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128284860</v>
+        <v>128278595</v>
       </c>
       <c r="B77" t="n">
-        <v>92668</v>
+        <v>80188</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8728,37 +8728,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4368</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547847</v>
+        <v>547811</v>
       </c>
       <c r="R77" t="n">
-        <v>6960134</v>
+        <v>6960055</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,64 +8812,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128278726</v>
+        <v>128284860</v>
       </c>
       <c r="B78" t="n">
-        <v>98478</v>
+        <v>92760</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547806</v>
+        <v>547847</v>
       </c>
       <c r="R78" t="n">
-        <v>6960028</v>
+        <v>6960134</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8898,7 +8894,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8908,7 +8904,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8923,57 +8919,61 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278595</v>
+        <v>128278726</v>
       </c>
       <c r="B79" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547811</v>
+        <v>547806</v>
       </c>
       <c r="R79" t="n">
-        <v>6960055</v>
+        <v>6960028</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,57 +9030,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128277499</v>
+        <v>128280541</v>
       </c>
       <c r="B80" t="n">
-        <v>80135</v>
+        <v>92026</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>547884</v>
+        <v>547656</v>
       </c>
       <c r="R80" t="n">
-        <v>6960163</v>
+        <v>6960341</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9110,19 +9110,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9137,60 +9127,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128284867</v>
+        <v>128277499</v>
       </c>
       <c r="B81" t="n">
-        <v>80164</v>
+        <v>80188</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>547611</v>
+        <v>547884</v>
       </c>
       <c r="R81" t="n">
-        <v>6960292</v>
+        <v>6960163</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9219,7 +9209,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9229,7 +9219,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9244,44 +9234,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128284866</v>
+        <v>128284867</v>
       </c>
       <c r="B82" t="n">
-        <v>80135</v>
+        <v>80217</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9294,10 +9284,10 @@
         <v>547611</v>
       </c>
       <c r="R82" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9363,32 +9353,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128280541</v>
+        <v>128284866</v>
       </c>
       <c r="B83" t="n">
-        <v>91934</v>
+        <v>80188</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9398,10 +9388,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R83" t="n">
-        <v>6960341</v>
+        <v>6960291</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9431,9 +9421,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9448,12 +9448,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9463,7 +9463,7 @@
         <v>128277635</v>
       </c>
       <c r="B84" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>128279138</v>
       </c>
       <c r="B85" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>128277916</v>
       </c>
       <c r="B86" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9791,52 +9791,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128278910</v>
+        <v>128284862</v>
       </c>
       <c r="B87" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>547750</v>
+        <v>547776</v>
       </c>
       <c r="R87" t="n">
-        <v>6960045</v>
+        <v>6960134</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9865,7 +9861,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9875,7 +9871,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9890,22 +9891,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128278608</v>
+        <v>128278910</v>
       </c>
       <c r="B88" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9932,7 +9933,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9941,10 +9942,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>547814</v>
+        <v>547750</v>
       </c>
       <c r="R88" t="n">
-        <v>6960059</v>
+        <v>6960045</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9976,7 +9977,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9986,7 +9987,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10013,10 +10014,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128279883</v>
+        <v>128278608</v>
       </c>
       <c r="B89" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10043,19 +10044,19 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>547596</v>
+        <v>547814</v>
       </c>
       <c r="R89" t="n">
-        <v>6960103</v>
+        <v>6960059</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10085,9 +10086,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10102,60 +10113,64 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128284862</v>
+        <v>128279883</v>
       </c>
       <c r="B90" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>547776</v>
+        <v>547596</v>
       </c>
       <c r="R90" t="n">
-        <v>6960134</v>
+        <v>6960103</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10182,24 +10197,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10214,22 +10214,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128279287</v>
+        <v>128279069</v>
       </c>
       <c r="B91" t="n">
-        <v>91656</v>
+        <v>80188</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,21 +10237,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547607</v>
+        <v>547670</v>
       </c>
       <c r="R91" t="n">
-        <v>6960041</v>
+        <v>6960031</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10333,10 +10333,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128279069</v>
+        <v>128279287</v>
       </c>
       <c r="B92" t="n">
-        <v>80135</v>
+        <v>91748</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10344,21 +10344,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>547670</v>
+        <v>547607</v>
       </c>
       <c r="R92" t="n">
-        <v>6960031</v>
+        <v>6960041</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10443,7 +10443,7 @@
         <v>128284863</v>
       </c>
       <c r="B93" t="n">
-        <v>56855</v>
+        <v>56867</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>128279518</v>
       </c>
       <c r="B94" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>128280491</v>
       </c>
       <c r="B95" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>128278124</v>
       </c>
       <c r="B96" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6233,48 +6233,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128284865</v>
+        <v>128279532</v>
       </c>
       <c r="B54" t="n">
-        <v>98592</v>
+        <v>57685</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547591</v>
+        <v>547624</v>
       </c>
       <c r="R54" t="n">
-        <v>6960277</v>
+        <v>6960008</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6303,7 +6308,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6313,7 +6318,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6328,19 +6338,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128278869</v>
+        <v>128278960</v>
       </c>
       <c r="B55" t="n">
         <v>98571</v>
@@ -6370,12 +6380,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6384,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547767</v>
+        <v>547724</v>
       </c>
       <c r="R55" t="n">
-        <v>6960048</v>
+        <v>6960039</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6419,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6429,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6444,19 +6449,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128278960</v>
+        <v>128278869</v>
       </c>
       <c r="B56" t="n">
         <v>98571</v>
@@ -6486,7 +6491,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6495,10 +6505,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547724</v>
+        <v>547767</v>
       </c>
       <c r="R56" t="n">
-        <v>6960039</v>
+        <v>6960048</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6530,7 +6540,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6540,7 +6550,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6555,65 +6565,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128279532</v>
+        <v>128284865</v>
       </c>
       <c r="B57" t="n">
-        <v>57685</v>
+        <v>98592</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547624</v>
+        <v>547591</v>
       </c>
       <c r="R57" t="n">
-        <v>6960008</v>
+        <v>6960277</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6642,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6652,12 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,12 +6672,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7111,48 +7111,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128279022</v>
+        <v>128284859</v>
       </c>
       <c r="B62" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547715</v>
+        <v>547891</v>
       </c>
       <c r="R62" t="n">
-        <v>6960022</v>
+        <v>6960165</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7206,60 +7206,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128284859</v>
+        <v>128279022</v>
       </c>
       <c r="B63" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547891</v>
+        <v>547715</v>
       </c>
       <c r="R63" t="n">
-        <v>6960165</v>
+        <v>6960022</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7313,19 +7313,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B64" t="n">
         <v>98571</v>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R64" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,7 +7432,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B65" t="n">
         <v>98571</v>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R65" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8494,52 +8494,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B75" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R75" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8568,7 +8564,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8578,7 +8574,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8593,60 +8594,64 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B76" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R76" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8675,7 +8680,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8685,12 +8690,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,57 +8705,61 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128278595</v>
+        <v>128278726</v>
       </c>
       <c r="B77" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547811</v>
+        <v>547806</v>
       </c>
       <c r="R77" t="n">
-        <v>6960055</v>
+        <v>6960028</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8787,7 +8791,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8797,7 +8801,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,12 +8816,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8931,49 +8935,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278726</v>
+        <v>128278595</v>
       </c>
       <c r="B79" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547806</v>
+        <v>547811</v>
       </c>
       <c r="R79" t="n">
-        <v>6960028</v>
+        <v>6960055</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,12 +9030,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10226,10 +10226,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128279069</v>
+        <v>128284863</v>
       </c>
       <c r="B91" t="n">
-        <v>80188</v>
+        <v>56867</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,37 +10237,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547670</v>
+        <v>547756</v>
       </c>
       <c r="R91" t="n">
-        <v>6960031</v>
+        <v>6960112</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10321,12 +10321,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10440,10 +10440,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128284863</v>
+        <v>128279069</v>
       </c>
       <c r="B93" t="n">
-        <v>56867</v>
+        <v>80188</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,37 +10451,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547756</v>
+        <v>547670</v>
       </c>
       <c r="R93" t="n">
-        <v>6960112</v>
+        <v>6960031</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,12 +10535,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10879,6 +10879,200 @@
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128622886</v>
+      </c>
+      <c r="B97" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>547595</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6960071</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128622883</v>
+      </c>
+      <c r="B98" t="n">
+        <v>80189</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>547595</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6960078</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6350,52 +6350,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128278960</v>
+        <v>128284865</v>
       </c>
       <c r="B55" t="n">
-        <v>98571</v>
+        <v>98592</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547724</v>
+        <v>547591</v>
       </c>
       <c r="R55" t="n">
-        <v>6960039</v>
+        <v>6960277</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6424,7 +6420,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6430,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6449,12 +6445,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6577,48 +6573,52 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128284865</v>
+        <v>128278960</v>
       </c>
       <c r="B57" t="n">
-        <v>98592</v>
+        <v>98571</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547591</v>
+        <v>547724</v>
       </c>
       <c r="R57" t="n">
-        <v>6960277</v>
+        <v>6960039</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,12 +6672,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B64" t="n">
         <v>98571</v>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R64" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,7 +7432,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B65" t="n">
         <v>98571</v>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R65" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7636,7 +7636,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B67" t="n">
         <v>57685</v>
@@ -7676,10 +7676,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R67" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7743,7 +7743,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128280133</v>
+        <v>128280081</v>
       </c>
       <c r="B68" t="n">
         <v>57685</v>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547601</v>
+        <v>547586</v>
       </c>
       <c r="R68" t="n">
-        <v>6960267</v>
+        <v>6960259</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8717,49 +8717,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128278726</v>
+        <v>128278595</v>
       </c>
       <c r="B77" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547806</v>
+        <v>547811</v>
       </c>
       <c r="R77" t="n">
-        <v>6960028</v>
+        <v>6960055</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8791,7 +8787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8801,7 +8797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,60 +8812,64 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128284860</v>
+        <v>128278726</v>
       </c>
       <c r="B78" t="n">
-        <v>92760</v>
+        <v>98571</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547847</v>
+        <v>547806</v>
       </c>
       <c r="R78" t="n">
-        <v>6960134</v>
+        <v>6960028</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8923,22 +8923,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278595</v>
+        <v>128284860</v>
       </c>
       <c r="B79" t="n">
-        <v>80188</v>
+        <v>92760</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8946,37 +8946,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>4368</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547811</v>
+        <v>547847</v>
       </c>
       <c r="R79" t="n">
-        <v>6960055</v>
+        <v>6960134</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,57 +9030,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128280541</v>
+        <v>128277499</v>
       </c>
       <c r="B80" t="n">
-        <v>92026</v>
+        <v>80188</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>547656</v>
+        <v>547884</v>
       </c>
       <c r="R80" t="n">
-        <v>6960341</v>
+        <v>6960163</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9110,9 +9110,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9127,60 +9137,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128277499</v>
+        <v>128284867</v>
       </c>
       <c r="B81" t="n">
-        <v>80188</v>
+        <v>80217</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>547884</v>
+        <v>547611</v>
       </c>
       <c r="R81" t="n">
-        <v>6960163</v>
+        <v>6960292</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9209,7 +9219,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9219,7 +9229,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9234,44 +9244,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128284867</v>
+        <v>128284866</v>
       </c>
       <c r="B82" t="n">
-        <v>80217</v>
+        <v>80188</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9284,10 +9294,10 @@
         <v>547611</v>
       </c>
       <c r="R82" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9353,32 +9363,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128284866</v>
+        <v>128280541</v>
       </c>
       <c r="B83" t="n">
-        <v>80188</v>
+        <v>92026</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9388,10 +9398,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R83" t="n">
-        <v>6960291</v>
+        <v>6960341</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,19 +9431,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9448,12 +9448,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9791,48 +9791,52 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128284862</v>
+        <v>128278910</v>
       </c>
       <c r="B87" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>547776</v>
+        <v>547750</v>
       </c>
       <c r="R87" t="n">
-        <v>6960134</v>
+        <v>6960045</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9861,7 +9865,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9871,12 +9875,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9891,19 +9890,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128278910</v>
+        <v>128278608</v>
       </c>
       <c r="B88" t="n">
         <v>98571</v>
@@ -9933,7 +9932,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9942,10 +9941,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>547750</v>
+        <v>547814</v>
       </c>
       <c r="R88" t="n">
-        <v>6960045</v>
+        <v>6960059</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9977,7 +9976,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9987,7 +9986,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10014,7 +10013,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128278608</v>
+        <v>128279883</v>
       </c>
       <c r="B89" t="n">
         <v>98571</v>
@@ -10044,19 +10043,19 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>547814</v>
+        <v>547596</v>
       </c>
       <c r="R89" t="n">
-        <v>6960059</v>
+        <v>6960103</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10086,19 +10085,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10113,64 +10102,60 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128279883</v>
+        <v>128284862</v>
       </c>
       <c r="B90" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>547596</v>
+        <v>547776</v>
       </c>
       <c r="R90" t="n">
-        <v>6960103</v>
+        <v>6960134</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10197,9 +10182,24 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10214,22 +10214,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128284863</v>
+        <v>128279069</v>
       </c>
       <c r="B91" t="n">
-        <v>56867</v>
+        <v>80188</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,37 +10237,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547756</v>
+        <v>547670</v>
       </c>
       <c r="R91" t="n">
-        <v>6960112</v>
+        <v>6960031</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10321,12 +10321,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10440,10 +10440,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128279069</v>
+        <v>128284863</v>
       </c>
       <c r="B93" t="n">
-        <v>80188</v>
+        <v>56867</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,37 +10451,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547670</v>
+        <v>547756</v>
       </c>
       <c r="R93" t="n">
-        <v>6960031</v>
+        <v>6960112</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,12 +10535,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -7111,48 +7111,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128284859</v>
+        <v>128279022</v>
       </c>
       <c r="B62" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547891</v>
+        <v>547715</v>
       </c>
       <c r="R62" t="n">
-        <v>6960165</v>
+        <v>6960022</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7206,60 +7206,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128279022</v>
+        <v>128284859</v>
       </c>
       <c r="B63" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547715</v>
+        <v>547891</v>
       </c>
       <c r="R63" t="n">
-        <v>6960022</v>
+        <v>6960165</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7313,12 +7313,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7850,52 +7850,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128278944</v>
+        <v>128284861</v>
       </c>
       <c r="B69" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547605</v>
+        <v>547812</v>
       </c>
       <c r="R69" t="n">
-        <v>6960074</v>
+        <v>6960137</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7924,7 +7920,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7934,7 +7930,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7949,60 +7945,64 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128284861</v>
+        <v>128278944</v>
       </c>
       <c r="B70" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547812</v>
+        <v>547605</v>
       </c>
       <c r="R70" t="n">
-        <v>6960137</v>
+        <v>6960074</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8056,12 +8056,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8494,48 +8494,52 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B75" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R75" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8564,7 +8568,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8574,12 +8578,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8594,64 +8593,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B76" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R76" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8680,7 +8675,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8690,7 +8685,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,22 +8705,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128278595</v>
+        <v>128284860</v>
       </c>
       <c r="B77" t="n">
-        <v>80188</v>
+        <v>92760</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8728,37 +8728,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>4368</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547811</v>
+        <v>547847</v>
       </c>
       <c r="R77" t="n">
-        <v>6960055</v>
+        <v>6960134</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,61 +8812,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128278726</v>
+        <v>128278595</v>
       </c>
       <c r="B78" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547806</v>
+        <v>547811</v>
       </c>
       <c r="R78" t="n">
-        <v>6960028</v>
+        <v>6960055</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8898,7 +8894,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8908,7 +8904,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8923,60 +8919,64 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128284860</v>
+        <v>128278726</v>
       </c>
       <c r="B79" t="n">
-        <v>92760</v>
+        <v>98571</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547847</v>
+        <v>547806</v>
       </c>
       <c r="R79" t="n">
-        <v>6960134</v>
+        <v>6960028</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,12 +9030,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9791,52 +9791,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128278910</v>
+        <v>128284862</v>
       </c>
       <c r="B87" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>547750</v>
+        <v>547776</v>
       </c>
       <c r="R87" t="n">
-        <v>6960045</v>
+        <v>6960134</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9865,7 +9861,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9875,7 +9871,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9890,19 +9891,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128278608</v>
+        <v>128278910</v>
       </c>
       <c r="B88" t="n">
         <v>98571</v>
@@ -9932,7 +9933,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9941,10 +9942,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>547814</v>
+        <v>547750</v>
       </c>
       <c r="R88" t="n">
-        <v>6960059</v>
+        <v>6960045</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9976,7 +9977,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9986,7 +9987,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10013,7 +10014,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128279883</v>
+        <v>128278608</v>
       </c>
       <c r="B89" t="n">
         <v>98571</v>
@@ -10043,19 +10044,19 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>547596</v>
+        <v>547814</v>
       </c>
       <c r="R89" t="n">
-        <v>6960103</v>
+        <v>6960059</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10085,9 +10086,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10102,60 +10113,64 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128284862</v>
+        <v>128279883</v>
       </c>
       <c r="B90" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>547776</v>
+        <v>547596</v>
       </c>
       <c r="R90" t="n">
-        <v>6960134</v>
+        <v>6960103</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10182,24 +10197,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10214,22 +10214,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128279069</v>
+        <v>128284863</v>
       </c>
       <c r="B91" t="n">
-        <v>80188</v>
+        <v>56867</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,37 +10237,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547670</v>
+        <v>547756</v>
       </c>
       <c r="R91" t="n">
-        <v>6960031</v>
+        <v>6960112</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10321,12 +10321,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10440,10 +10440,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128284863</v>
+        <v>128279069</v>
       </c>
       <c r="B93" t="n">
-        <v>56867</v>
+        <v>80188</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,37 +10451,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547756</v>
+        <v>547670</v>
       </c>
       <c r="R93" t="n">
-        <v>6960112</v>
+        <v>6960031</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,12 +10535,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10884,7 +10884,7 @@
         <v>128622886</v>
       </c>
       <c r="B97" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>128622883</v>
       </c>
       <c r="B98" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6032,7 +6032,7 @@
         <v>128278178</v>
       </c>
       <c r="B52" t="n">
-        <v>92026</v>
+        <v>92038</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6126,45 +6126,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128278898</v>
+        <v>128278869</v>
       </c>
       <c r="B53" t="n">
-        <v>80188</v>
+        <v>98585</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547758</v>
+        <v>547767</v>
       </c>
       <c r="R53" t="n">
-        <v>6960041</v>
+        <v>6960048</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6196,7 +6205,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6206,7 +6215,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6233,50 +6242,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128279532</v>
+        <v>128278960</v>
       </c>
       <c r="B54" t="n">
-        <v>57685</v>
+        <v>98585</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547624</v>
+        <v>547724</v>
       </c>
       <c r="R54" t="n">
-        <v>6960008</v>
+        <v>6960039</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6308,7 +6316,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6318,12 +6326,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6338,60 +6341,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128284865</v>
+        <v>128278898</v>
       </c>
       <c r="B55" t="n">
-        <v>98592</v>
+        <v>80192</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547591</v>
+        <v>547758</v>
       </c>
       <c r="R55" t="n">
-        <v>6960277</v>
+        <v>6960041</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6420,7 +6423,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6430,7 +6433,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6445,66 +6448,62 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128278869</v>
+        <v>128279532</v>
       </c>
       <c r="B56" t="n">
-        <v>98571</v>
+        <v>57689</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547767</v>
+        <v>547624</v>
       </c>
       <c r="R56" t="n">
-        <v>6960048</v>
+        <v>6960008</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6535,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6546,7 +6545,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6573,52 +6577,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128278960</v>
+        <v>128284865</v>
       </c>
       <c r="B57" t="n">
-        <v>98571</v>
+        <v>98606</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547724</v>
+        <v>547591</v>
       </c>
       <c r="R57" t="n">
-        <v>6960039</v>
+        <v>6960277</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,12 +6672,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
         <v>128279150</v>
       </c>
       <c r="B58" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>128279511</v>
       </c>
       <c r="B59" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>128277912</v>
       </c>
       <c r="B60" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>128284869</v>
       </c>
       <c r="B61" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7111,48 +7111,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128279022</v>
+        <v>128284859</v>
       </c>
       <c r="B62" t="n">
-        <v>80188</v>
+        <v>98585</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547715</v>
+        <v>547891</v>
       </c>
       <c r="R62" t="n">
-        <v>6960022</v>
+        <v>6960165</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7206,60 +7206,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128284859</v>
+        <v>128279022</v>
       </c>
       <c r="B63" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547891</v>
+        <v>547715</v>
       </c>
       <c r="R63" t="n">
-        <v>6960165</v>
+        <v>6960022</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7313,12 +7313,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7328,7 +7328,7 @@
         <v>128284868</v>
       </c>
       <c r="B64" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>128284872</v>
       </c>
       <c r="B65" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>128279803</v>
       </c>
       <c r="B66" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7636,10 +7636,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128280133</v>
+        <v>128280081</v>
       </c>
       <c r="B67" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7676,10 +7676,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547601</v>
+        <v>547586</v>
       </c>
       <c r="R67" t="n">
-        <v>6960267</v>
+        <v>6960259</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B68" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R68" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7853,7 +7853,7 @@
         <v>128284861</v>
       </c>
       <c r="B69" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>128278944</v>
       </c>
       <c r="B70" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>128284870</v>
       </c>
       <c r="B71" t="n">
-        <v>92149</v>
+        <v>92161</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>128278487</v>
       </c>
       <c r="B72" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>128279241</v>
       </c>
       <c r="B73" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>128279186</v>
       </c>
       <c r="B74" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8494,52 +8494,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B75" t="n">
-        <v>98571</v>
+        <v>57849</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R75" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8568,7 +8564,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8578,7 +8574,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8593,60 +8594,64 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B76" t="n">
-        <v>57845</v>
+        <v>98585</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R76" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8675,7 +8680,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8685,12 +8690,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,12 +8705,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8720,7 +8720,7 @@
         <v>128284860</v>
       </c>
       <c r="B77" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8824,45 +8824,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128278595</v>
+        <v>128278726</v>
       </c>
       <c r="B78" t="n">
-        <v>80188</v>
+        <v>98585</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547811</v>
+        <v>547806</v>
       </c>
       <c r="R78" t="n">
-        <v>6960055</v>
+        <v>6960028</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8894,7 +8898,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8904,7 +8908,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8919,61 +8923,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278726</v>
+        <v>128278595</v>
       </c>
       <c r="B79" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547806</v>
+        <v>547811</v>
       </c>
       <c r="R79" t="n">
-        <v>6960028</v>
+        <v>6960055</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,60 +9030,60 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128277499</v>
+        <v>128284867</v>
       </c>
       <c r="B80" t="n">
-        <v>80188</v>
+        <v>80221</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>547884</v>
+        <v>547611</v>
       </c>
       <c r="R80" t="n">
-        <v>6960163</v>
+        <v>6960292</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9137,44 +9137,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128284867</v>
+        <v>128284866</v>
       </c>
       <c r="B81" t="n">
-        <v>80217</v>
+        <v>80192</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9187,10 +9187,10 @@
         <v>547611</v>
       </c>
       <c r="R81" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9256,32 +9256,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128284866</v>
+        <v>128280541</v>
       </c>
       <c r="B82" t="n">
-        <v>80188</v>
+        <v>92038</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R82" t="n">
-        <v>6960291</v>
+        <v>6960341</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9324,19 +9324,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,57 +9341,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128280541</v>
+        <v>128277499</v>
       </c>
       <c r="B83" t="n">
-        <v>92026</v>
+        <v>80192</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>547656</v>
+        <v>547884</v>
       </c>
       <c r="R83" t="n">
-        <v>6960341</v>
+        <v>6960163</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9431,9 +9421,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9448,57 +9448,62 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128277635</v>
+        <v>128279138</v>
       </c>
       <c r="B84" t="n">
-        <v>92742</v>
+        <v>57689</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>547856</v>
+        <v>547548</v>
       </c>
       <c r="R84" t="n">
-        <v>6960149</v>
+        <v>6960061</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,19 +9533,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9555,62 +9555,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128279138</v>
+        <v>128277635</v>
       </c>
       <c r="B85" t="n">
-        <v>57685</v>
+        <v>92754</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>547548</v>
+        <v>547856</v>
       </c>
       <c r="R85" t="n">
-        <v>6960061</v>
+        <v>6960149</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9640,14 +9635,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9662,12 +9662,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9677,7 +9677,7 @@
         <v>128277916</v>
       </c>
       <c r="B86" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>128284862</v>
       </c>
       <c r="B87" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>128278910</v>
       </c>
       <c r="B88" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>128278608</v>
       </c>
       <c r="B89" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>128279883</v>
       </c>
       <c r="B90" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10226,10 +10226,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128284863</v>
+        <v>128279287</v>
       </c>
       <c r="B91" t="n">
-        <v>56867</v>
+        <v>91760</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,37 +10237,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547756</v>
+        <v>547607</v>
       </c>
       <c r="R91" t="n">
-        <v>6960112</v>
+        <v>6960041</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10321,22 +10321,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128279287</v>
+        <v>128284863</v>
       </c>
       <c r="B92" t="n">
-        <v>91748</v>
+        <v>56871</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10344,37 +10344,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>547607</v>
+        <v>547756</v>
       </c>
       <c r="R92" t="n">
-        <v>6960041</v>
+        <v>6960112</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10428,12 +10428,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10443,7 +10443,7 @@
         <v>128279069</v>
       </c>
       <c r="B93" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>128279518</v>
       </c>
       <c r="B94" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>128280491</v>
       </c>
       <c r="B95" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>128278124</v>
       </c>
       <c r="B96" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -7111,48 +7111,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128284859</v>
+        <v>128279022</v>
       </c>
       <c r="B62" t="n">
-        <v>98585</v>
+        <v>80192</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547891</v>
+        <v>547715</v>
       </c>
       <c r="R62" t="n">
-        <v>6960165</v>
+        <v>6960022</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7206,60 +7206,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128279022</v>
+        <v>128284859</v>
       </c>
       <c r="B63" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547715</v>
+        <v>547891</v>
       </c>
       <c r="R63" t="n">
-        <v>6960022</v>
+        <v>6960165</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7313,12 +7313,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8717,48 +8717,52 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128284860</v>
+        <v>128278726</v>
       </c>
       <c r="B77" t="n">
-        <v>92772</v>
+        <v>98585</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547847</v>
+        <v>547806</v>
       </c>
       <c r="R77" t="n">
-        <v>6960134</v>
+        <v>6960028</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8787,7 +8791,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8797,7 +8801,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,61 +8816,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128278726</v>
+        <v>128278595</v>
       </c>
       <c r="B78" t="n">
-        <v>98585</v>
+        <v>80192</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547806</v>
+        <v>547811</v>
       </c>
       <c r="R78" t="n">
-        <v>6960028</v>
+        <v>6960055</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8923,22 +8923,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278595</v>
+        <v>128284860</v>
       </c>
       <c r="B79" t="n">
-        <v>80192</v>
+        <v>92772</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8946,37 +8946,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>4368</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547811</v>
+        <v>547847</v>
       </c>
       <c r="R79" t="n">
-        <v>6960055</v>
+        <v>6960134</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,12 +9030,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9460,50 +9460,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128279138</v>
+        <v>128277635</v>
       </c>
       <c r="B84" t="n">
-        <v>57689</v>
+        <v>92754</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>547548</v>
+        <v>547856</v>
       </c>
       <c r="R84" t="n">
-        <v>6960061</v>
+        <v>6960149</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9533,14 +9528,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9555,57 +9555,62 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128277635</v>
+        <v>128279138</v>
       </c>
       <c r="B85" t="n">
-        <v>92754</v>
+        <v>57689</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>547856</v>
+        <v>547548</v>
       </c>
       <c r="R85" t="n">
-        <v>6960149</v>
+        <v>6960061</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,19 +9640,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9662,12 +9662,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10226,10 +10226,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128279287</v>
+        <v>128279069</v>
       </c>
       <c r="B91" t="n">
-        <v>91760</v>
+        <v>80192</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,21 +10237,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547607</v>
+        <v>547670</v>
       </c>
       <c r="R91" t="n">
-        <v>6960041</v>
+        <v>6960031</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10440,10 +10440,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128279069</v>
+        <v>128279287</v>
       </c>
       <c r="B93" t="n">
-        <v>80192</v>
+        <v>91760</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,21 +10451,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10475,10 +10475,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547670</v>
+        <v>547607</v>
       </c>
       <c r="R93" t="n">
-        <v>6960031</v>
+        <v>6960041</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD93" t="b">

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6032,7 +6032,7 @@
         <v>128278178</v>
       </c>
       <c r="B52" t="n">
-        <v>92038</v>
+        <v>92040</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6126,54 +6126,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128278869</v>
+        <v>128279532</v>
       </c>
       <c r="B53" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547767</v>
+        <v>547624</v>
       </c>
       <c r="R53" t="n">
-        <v>6960048</v>
+        <v>6960008</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6205,7 +6201,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6215,7 +6211,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,49 +6243,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128278960</v>
+        <v>128278898</v>
       </c>
       <c r="B54" t="n">
-        <v>98585</v>
+        <v>80194</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547724</v>
+        <v>547758</v>
       </c>
       <c r="R54" t="n">
-        <v>6960039</v>
+        <v>6960041</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6316,7 +6313,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6326,7 +6323,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6341,60 +6338,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128278898</v>
+        <v>128284865</v>
       </c>
       <c r="B55" t="n">
-        <v>80192</v>
+        <v>98609</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547758</v>
+        <v>547591</v>
       </c>
       <c r="R55" t="n">
-        <v>6960041</v>
+        <v>6960277</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6423,7 +6420,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6433,7 +6430,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6448,62 +6445,61 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128279532</v>
+        <v>128278960</v>
       </c>
       <c r="B56" t="n">
-        <v>57689</v>
+        <v>98588</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547624</v>
+        <v>547724</v>
       </c>
       <c r="R56" t="n">
-        <v>6960008</v>
+        <v>6960039</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6535,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6545,12 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6565,60 +6556,69 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128284865</v>
+        <v>128278869</v>
       </c>
       <c r="B57" t="n">
-        <v>98606</v>
+        <v>98588</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547591</v>
+        <v>547767</v>
       </c>
       <c r="R57" t="n">
-        <v>6960277</v>
+        <v>6960048</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,12 +6672,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
         <v>128279150</v>
       </c>
       <c r="B58" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>128279511</v>
       </c>
       <c r="B59" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>128277912</v>
       </c>
       <c r="B60" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>128284869</v>
       </c>
       <c r="B61" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>128279022</v>
       </c>
       <c r="B62" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>128284859</v>
       </c>
       <c r="B63" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7325,10 +7325,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B64" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R64" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,10 +7432,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B65" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R65" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7539,10 +7539,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128279803</v>
+        <v>128280081</v>
       </c>
       <c r="B66" t="n">
-        <v>92748</v>
+        <v>57689</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7550,34 +7550,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547600</v>
+        <v>547586</v>
       </c>
       <c r="R66" t="n">
-        <v>6960084</v>
+        <v>6960259</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7610,6 +7615,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7636,7 +7646,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B67" t="n">
         <v>57689</v>
@@ -7676,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R67" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7743,10 +7753,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128280133</v>
+        <v>128279803</v>
       </c>
       <c r="B68" t="n">
-        <v>57689</v>
+        <v>92750</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7754,39 +7764,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547601</v>
+        <v>547600</v>
       </c>
       <c r="R68" t="n">
-        <v>6960267</v>
+        <v>6960084</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7819,11 +7824,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7853,7 +7853,7 @@
         <v>128284861</v>
       </c>
       <c r="B69" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>128278944</v>
       </c>
       <c r="B70" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>128284870</v>
       </c>
       <c r="B71" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>128279241</v>
       </c>
       <c r="B73" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>128279186</v>
       </c>
       <c r="B74" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>128278988</v>
       </c>
       <c r="B76" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8717,52 +8717,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128278726</v>
+        <v>128284860</v>
       </c>
       <c r="B77" t="n">
-        <v>98585</v>
+        <v>92774</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547806</v>
+        <v>547847</v>
       </c>
       <c r="R77" t="n">
-        <v>6960028</v>
+        <v>6960134</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8791,7 +8787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8801,7 +8797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,12 +8812,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8831,7 +8827,7 @@
         <v>128278595</v>
       </c>
       <c r="B78" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8935,48 +8931,52 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128284860</v>
+        <v>128278726</v>
       </c>
       <c r="B79" t="n">
-        <v>92772</v>
+        <v>98588</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547847</v>
+        <v>547806</v>
       </c>
       <c r="R79" t="n">
-        <v>6960134</v>
+        <v>6960028</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,44 +9030,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128284867</v>
+        <v>128280541</v>
       </c>
       <c r="B80" t="n">
-        <v>80221</v>
+        <v>92040</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9077,13 +9077,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R80" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9110,19 +9110,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9137,12 +9127,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9152,7 +9142,7 @@
         <v>128284866</v>
       </c>
       <c r="B81" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9256,45 +9246,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128280541</v>
+        <v>128277499</v>
       </c>
       <c r="B82" t="n">
-        <v>92038</v>
+        <v>80194</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>547656</v>
+        <v>547884</v>
       </c>
       <c r="R82" t="n">
-        <v>6960341</v>
+        <v>6960163</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9324,9 +9314,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9341,60 +9341,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128277499</v>
+        <v>128284867</v>
       </c>
       <c r="B83" t="n">
-        <v>80192</v>
+        <v>80223</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>547884</v>
+        <v>547611</v>
       </c>
       <c r="R83" t="n">
-        <v>6960163</v>
+        <v>6960292</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9448,12 +9448,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9463,7 +9463,7 @@
         <v>128277635</v>
       </c>
       <c r="B84" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>128284862</v>
       </c>
       <c r="B87" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>128278910</v>
       </c>
       <c r="B88" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>128278608</v>
       </c>
       <c r="B89" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>128279883</v>
       </c>
       <c r="B90" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10226,10 +10226,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128279069</v>
+        <v>128279287</v>
       </c>
       <c r="B91" t="n">
-        <v>80192</v>
+        <v>91762</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,21 +10237,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547670</v>
+        <v>547607</v>
       </c>
       <c r="R91" t="n">
-        <v>6960031</v>
+        <v>6960041</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10333,10 +10333,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128284863</v>
+        <v>128279069</v>
       </c>
       <c r="B92" t="n">
-        <v>56871</v>
+        <v>80194</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10344,37 +10344,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>547756</v>
+        <v>547670</v>
       </c>
       <c r="R92" t="n">
-        <v>6960112</v>
+        <v>6960031</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10428,22 +10428,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128279287</v>
+        <v>128284863</v>
       </c>
       <c r="B93" t="n">
-        <v>91760</v>
+        <v>56871</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,37 +10451,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547607</v>
+        <v>547756</v>
       </c>
       <c r="R93" t="n">
-        <v>6960041</v>
+        <v>6960112</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,12 +10535,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
         <v>128279518</v>
       </c>
       <c r="B94" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>128278124</v>
       </c>
       <c r="B96" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>128622886</v>
       </c>
       <c r="B97" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>128622883</v>
       </c>
       <c r="B98" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6353,7 +6353,7 @@
         <v>128284865</v>
       </c>
       <c r="B55" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>128278960</v>
       </c>
       <c r="B56" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>128278869</v>
       </c>
       <c r="B57" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6684,45 +6684,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128279150</v>
+        <v>128279511</v>
       </c>
       <c r="B58" t="n">
-        <v>92748</v>
+        <v>98591</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547640</v>
+        <v>547618</v>
       </c>
       <c r="R58" t="n">
-        <v>6960059</v>
+        <v>6960012</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6754,7 +6763,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6764,7 +6773,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6779,66 +6788,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128279511</v>
+        <v>128279150</v>
       </c>
       <c r="B59" t="n">
-        <v>98588</v>
+        <v>92748</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547618</v>
+        <v>547640</v>
       </c>
       <c r="R59" t="n">
-        <v>6960012</v>
+        <v>6960059</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6895,12 +6895,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7111,48 +7111,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128279022</v>
+        <v>128284859</v>
       </c>
       <c r="B62" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547715</v>
+        <v>547891</v>
       </c>
       <c r="R62" t="n">
-        <v>6960022</v>
+        <v>6960165</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7206,60 +7206,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128284859</v>
+        <v>128279022</v>
       </c>
       <c r="B63" t="n">
-        <v>98588</v>
+        <v>80194</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547891</v>
+        <v>547715</v>
       </c>
       <c r="R63" t="n">
-        <v>6960165</v>
+        <v>6960022</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7313,12 +7313,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7328,7 +7328,7 @@
         <v>128284872</v>
       </c>
       <c r="B64" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>128284868</v>
       </c>
       <c r="B65" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128280081</v>
+        <v>128279803</v>
       </c>
       <c r="B66" t="n">
-        <v>57689</v>
+        <v>92750</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7550,39 +7550,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547586</v>
+        <v>547600</v>
       </c>
       <c r="R66" t="n">
-        <v>6960259</v>
+        <v>6960084</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7615,11 +7610,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7646,7 +7636,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128280133</v>
+        <v>128280081</v>
       </c>
       <c r="B67" t="n">
         <v>57689</v>
@@ -7686,10 +7676,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547601</v>
+        <v>547586</v>
       </c>
       <c r="R67" t="n">
-        <v>6960267</v>
+        <v>6960259</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7753,10 +7743,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128279803</v>
+        <v>128280133</v>
       </c>
       <c r="B68" t="n">
-        <v>92750</v>
+        <v>57689</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7764,34 +7754,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547600</v>
+        <v>547601</v>
       </c>
       <c r="R68" t="n">
-        <v>6960084</v>
+        <v>6960267</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7824,6 +7819,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7850,48 +7850,52 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128284861</v>
+        <v>128278944</v>
       </c>
       <c r="B69" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547812</v>
+        <v>547605</v>
       </c>
       <c r="R69" t="n">
-        <v>6960137</v>
+        <v>6960074</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7920,7 +7924,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7930,7 +7934,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7945,64 +7949,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128278944</v>
+        <v>128284861</v>
       </c>
       <c r="B70" t="n">
-        <v>98588</v>
+        <v>80194</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547605</v>
+        <v>547812</v>
       </c>
       <c r="R70" t="n">
-        <v>6960074</v>
+        <v>6960137</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8056,60 +8056,65 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128284870</v>
+        <v>128278487</v>
       </c>
       <c r="B71" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547621</v>
+        <v>547771</v>
       </c>
       <c r="R71" t="n">
-        <v>6960289</v>
+        <v>6960077</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8136,19 +8141,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,62 +8163,61 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128278487</v>
+        <v>128279241</v>
       </c>
       <c r="B72" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547771</v>
+        <v>547618</v>
       </c>
       <c r="R72" t="n">
-        <v>6960077</v>
+        <v>6960049</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8248,14 +8247,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8270,22 +8274,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128279241</v>
+        <v>128279186</v>
       </c>
       <c r="B73" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8317,14 +8321,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>547618</v>
+        <v>547558</v>
       </c>
       <c r="R73" t="n">
-        <v>6960049</v>
+        <v>6960050</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8354,19 +8358,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8381,64 +8375,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128279186</v>
+        <v>128284870</v>
       </c>
       <c r="B74" t="n">
-        <v>98588</v>
+        <v>92163</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>547558</v>
+        <v>547621</v>
       </c>
       <c r="R74" t="n">
-        <v>6960050</v>
+        <v>6960289</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8465,9 +8455,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8482,12 +8482,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8609,7 +8609,7 @@
         <v>128278988</v>
       </c>
       <c r="B76" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8824,45 +8824,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128278595</v>
+        <v>128278726</v>
       </c>
       <c r="B78" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547811</v>
+        <v>547806</v>
       </c>
       <c r="R78" t="n">
-        <v>6960055</v>
+        <v>6960028</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8894,7 +8898,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8904,7 +8908,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8919,61 +8923,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278726</v>
+        <v>128278595</v>
       </c>
       <c r="B79" t="n">
-        <v>98588</v>
+        <v>80194</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547806</v>
+        <v>547811</v>
       </c>
       <c r="R79" t="n">
-        <v>6960028</v>
+        <v>6960055</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,57 +9030,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128280541</v>
+        <v>128277499</v>
       </c>
       <c r="B80" t="n">
-        <v>92040</v>
+        <v>80194</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>547656</v>
+        <v>547884</v>
       </c>
       <c r="R80" t="n">
-        <v>6960341</v>
+        <v>6960163</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9110,9 +9110,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9127,44 +9137,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128284866</v>
+        <v>128284867</v>
       </c>
       <c r="B81" t="n">
-        <v>80194</v>
+        <v>80223</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9177,10 +9187,10 @@
         <v>547611</v>
       </c>
       <c r="R81" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9246,7 +9256,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128277499</v>
+        <v>128284866</v>
       </c>
       <c r="B82" t="n">
         <v>80194</v>
@@ -9277,14 +9287,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>547884</v>
+        <v>547611</v>
       </c>
       <c r="R82" t="n">
-        <v>6960163</v>
+        <v>6960291</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9316,7 +9326,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9326,7 +9336,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9341,44 +9351,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128284867</v>
+        <v>128280541</v>
       </c>
       <c r="B83" t="n">
-        <v>80223</v>
+        <v>92040</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9388,13 +9398,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R83" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9421,19 +9431,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9448,12 +9448,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9906,7 +9906,7 @@
         <v>128278910</v>
       </c>
       <c r="B88" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>128278608</v>
       </c>
       <c r="B89" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>128279883</v>
       </c>
       <c r="B90" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>128279518</v>
       </c>
       <c r="B94" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>128278124</v>
       </c>
       <c r="B96" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6126,10 +6126,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128279532</v>
+        <v>128278898</v>
       </c>
       <c r="B53" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6137,39 +6137,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547624</v>
+        <v>547758</v>
       </c>
       <c r="R53" t="n">
-        <v>6960008</v>
+        <v>6960041</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6201,7 +6196,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6211,12 +6206,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6243,10 +6233,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128278898</v>
+        <v>128279532</v>
       </c>
       <c r="B54" t="n">
-        <v>80194</v>
+        <v>57689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,34 +6244,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547758</v>
+        <v>547624</v>
       </c>
       <c r="R54" t="n">
-        <v>6960041</v>
+        <v>6960008</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6313,7 +6308,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6323,7 +6318,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7850,52 +7850,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128278944</v>
+        <v>128284861</v>
       </c>
       <c r="B69" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547605</v>
+        <v>547812</v>
       </c>
       <c r="R69" t="n">
-        <v>6960074</v>
+        <v>6960137</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7924,7 +7920,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7934,7 +7930,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7949,60 +7945,64 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128284861</v>
+        <v>128278944</v>
       </c>
       <c r="B70" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547812</v>
+        <v>547605</v>
       </c>
       <c r="R70" t="n">
-        <v>6960137</v>
+        <v>6960074</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8056,65 +8056,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128278487</v>
+        <v>128284870</v>
       </c>
       <c r="B71" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547771</v>
+        <v>547621</v>
       </c>
       <c r="R71" t="n">
-        <v>6960077</v>
+        <v>6960289</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8141,14 +8136,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,61 +8163,62 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128279241</v>
+        <v>128278487</v>
       </c>
       <c r="B72" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547618</v>
+        <v>547771</v>
       </c>
       <c r="R72" t="n">
-        <v>6960049</v>
+        <v>6960077</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8247,19 +8248,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8274,19 +8270,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128279186</v>
+        <v>128279241</v>
       </c>
       <c r="B73" t="n">
         <v>98591</v>
@@ -8321,14 +8317,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>547558</v>
+        <v>547618</v>
       </c>
       <c r="R73" t="n">
-        <v>6960050</v>
+        <v>6960049</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8358,9 +8354,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8375,60 +8381,64 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128284870</v>
+        <v>128279186</v>
       </c>
       <c r="B74" t="n">
-        <v>92163</v>
+        <v>98591</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>547621</v>
+        <v>547558</v>
       </c>
       <c r="R74" t="n">
-        <v>6960289</v>
+        <v>6960050</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8455,19 +8465,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8482,12 +8482,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8717,48 +8717,52 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128284860</v>
+        <v>128278726</v>
       </c>
       <c r="B77" t="n">
-        <v>92774</v>
+        <v>98591</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547847</v>
+        <v>547806</v>
       </c>
       <c r="R77" t="n">
-        <v>6960134</v>
+        <v>6960028</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8787,7 +8791,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8797,7 +8801,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,64 +8816,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128278726</v>
+        <v>128284860</v>
       </c>
       <c r="B78" t="n">
-        <v>98591</v>
+        <v>92774</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547806</v>
+        <v>547847</v>
       </c>
       <c r="R78" t="n">
-        <v>6960028</v>
+        <v>6960134</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8923,12 +8923,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6032,7 +6032,7 @@
         <v>128278178</v>
       </c>
       <c r="B52" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6350,48 +6350,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128284865</v>
+        <v>128278960</v>
       </c>
       <c r="B55" t="n">
-        <v>98612</v>
+        <v>98592</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547591</v>
+        <v>547724</v>
       </c>
       <c r="R55" t="n">
-        <v>6960277</v>
+        <v>6960039</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6420,7 +6424,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6430,7 +6434,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6445,22 +6449,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128278960</v>
+        <v>128278869</v>
       </c>
       <c r="B56" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6487,7 +6491,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6496,10 +6505,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547724</v>
+        <v>547767</v>
       </c>
       <c r="R56" t="n">
-        <v>6960039</v>
+        <v>6960048</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6540,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6550,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6556,69 +6565,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128278869</v>
+        <v>128284865</v>
       </c>
       <c r="B57" t="n">
-        <v>98591</v>
+        <v>98613</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547767</v>
+        <v>547591</v>
       </c>
       <c r="R57" t="n">
-        <v>6960048</v>
+        <v>6960277</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,12 +6672,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
         <v>128279511</v>
       </c>
       <c r="B58" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>128279150</v>
       </c>
       <c r="B59" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7111,48 +7111,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128284859</v>
+        <v>128279022</v>
       </c>
       <c r="B62" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547891</v>
+        <v>547715</v>
       </c>
       <c r="R62" t="n">
-        <v>6960165</v>
+        <v>6960022</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7206,60 +7206,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128279022</v>
+        <v>128284859</v>
       </c>
       <c r="B63" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547715</v>
+        <v>547891</v>
       </c>
       <c r="R63" t="n">
-        <v>6960022</v>
+        <v>6960165</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7313,12 +7313,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7328,7 +7328,7 @@
         <v>128284872</v>
       </c>
       <c r="B64" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>128284868</v>
       </c>
       <c r="B65" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>128279803</v>
       </c>
       <c r="B66" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>128278944</v>
       </c>
       <c r="B70" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>128284870</v>
       </c>
       <c r="B71" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,50 +8175,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128278487</v>
+        <v>128279241</v>
       </c>
       <c r="B72" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547771</v>
+        <v>547618</v>
       </c>
       <c r="R72" t="n">
-        <v>6960077</v>
+        <v>6960049</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8248,14 +8247,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8270,22 +8274,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128279241</v>
+        <v>128279186</v>
       </c>
       <c r="B73" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8317,14 +8321,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>547618</v>
+        <v>547558</v>
       </c>
       <c r="R73" t="n">
-        <v>6960049</v>
+        <v>6960050</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8354,19 +8358,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8381,61 +8375,62 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128279186</v>
+        <v>128278487</v>
       </c>
       <c r="B74" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>547558</v>
+        <v>547771</v>
       </c>
       <c r="R74" t="n">
-        <v>6960050</v>
+        <v>6960077</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8468,6 +8463,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8494,48 +8494,52 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B75" t="n">
-        <v>57849</v>
+        <v>98592</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R75" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8564,7 +8568,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8574,12 +8578,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8594,64 +8593,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B76" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R76" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8680,7 +8675,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8690,7 +8685,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,64 +8705,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128278726</v>
+        <v>128284860</v>
       </c>
       <c r="B77" t="n">
-        <v>98591</v>
+        <v>92775</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547806</v>
+        <v>547847</v>
       </c>
       <c r="R77" t="n">
-        <v>6960028</v>
+        <v>6960134</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8791,7 +8787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8801,7 +8797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,22 +8812,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128284860</v>
+        <v>128278595</v>
       </c>
       <c r="B78" t="n">
-        <v>92774</v>
+        <v>80194</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8839,37 +8835,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4368</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547847</v>
+        <v>547811</v>
       </c>
       <c r="R78" t="n">
-        <v>6960134</v>
+        <v>6960055</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8898,7 +8894,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8908,7 +8904,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8923,57 +8919,61 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278595</v>
+        <v>128278726</v>
       </c>
       <c r="B79" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547811</v>
+        <v>547806</v>
       </c>
       <c r="R79" t="n">
-        <v>6960055</v>
+        <v>6960028</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,12 +9030,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9366,7 +9366,7 @@
         <v>128280541</v>
       </c>
       <c r="B83" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9460,45 +9460,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128277635</v>
+        <v>128279138</v>
       </c>
       <c r="B84" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>547856</v>
+        <v>547548</v>
       </c>
       <c r="R84" t="n">
-        <v>6960149</v>
+        <v>6960061</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,19 +9533,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9555,62 +9555,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128279138</v>
+        <v>128277635</v>
       </c>
       <c r="B85" t="n">
-        <v>57689</v>
+        <v>92757</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>547548</v>
+        <v>547856</v>
       </c>
       <c r="R85" t="n">
-        <v>6960061</v>
+        <v>6960149</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9640,14 +9635,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9662,12 +9662,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9791,48 +9791,52 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128284862</v>
+        <v>128278910</v>
       </c>
       <c r="B87" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>547776</v>
+        <v>547750</v>
       </c>
       <c r="R87" t="n">
-        <v>6960134</v>
+        <v>6960045</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9861,7 +9865,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9871,12 +9875,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9891,22 +9890,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128278910</v>
+        <v>128278608</v>
       </c>
       <c r="B88" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9933,7 +9932,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9942,10 +9941,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>547750</v>
+        <v>547814</v>
       </c>
       <c r="R88" t="n">
-        <v>6960045</v>
+        <v>6960059</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9977,7 +9976,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9987,7 +9986,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10014,10 +10013,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128278608</v>
+        <v>128279883</v>
       </c>
       <c r="B89" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10044,19 +10043,19 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>547814</v>
+        <v>547596</v>
       </c>
       <c r="R89" t="n">
-        <v>6960059</v>
+        <v>6960103</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10086,19 +10085,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10113,64 +10102,60 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128279883</v>
+        <v>128284862</v>
       </c>
       <c r="B90" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>547596</v>
+        <v>547776</v>
       </c>
       <c r="R90" t="n">
-        <v>6960103</v>
+        <v>6960134</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10197,9 +10182,24 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10214,12 +10214,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10229,7 +10229,7 @@
         <v>128279287</v>
       </c>
       <c r="B91" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>128279518</v>
       </c>
       <c r="B94" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>128278124</v>
       </c>
       <c r="B96" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6126,10 +6126,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128278898</v>
+        <v>128279532</v>
       </c>
       <c r="B53" t="n">
-        <v>80194</v>
+        <v>57689</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6137,34 +6137,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547758</v>
+        <v>547624</v>
       </c>
       <c r="R53" t="n">
-        <v>6960041</v>
+        <v>6960008</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6196,7 +6201,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6206,7 +6211,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6233,53 +6243,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128279532</v>
+        <v>128284865</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>98613</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547624</v>
+        <v>547591</v>
       </c>
       <c r="R54" t="n">
-        <v>6960008</v>
+        <v>6960277</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6308,7 +6313,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6318,12 +6323,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6338,61 +6338,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128278960</v>
+        <v>128278898</v>
       </c>
       <c r="B55" t="n">
-        <v>98592</v>
+        <v>80194</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547724</v>
+        <v>547758</v>
       </c>
       <c r="R55" t="n">
-        <v>6960039</v>
+        <v>6960041</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6424,7 +6420,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6434,7 +6430,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6449,19 +6445,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128278869</v>
+        <v>128278960</v>
       </c>
       <c r="B56" t="n">
         <v>98592</v>
@@ -6491,12 +6487,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6505,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547767</v>
+        <v>547724</v>
       </c>
       <c r="R56" t="n">
-        <v>6960048</v>
+        <v>6960039</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6540,7 +6531,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6550,7 +6541,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6565,60 +6556,69 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128284865</v>
+        <v>128278869</v>
       </c>
       <c r="B57" t="n">
-        <v>98613</v>
+        <v>98592</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547591</v>
+        <v>547767</v>
       </c>
       <c r="R57" t="n">
-        <v>6960277</v>
+        <v>6960048</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,12 +6672,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -10226,10 +10226,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128279287</v>
+        <v>128279069</v>
       </c>
       <c r="B91" t="n">
-        <v>91763</v>
+        <v>80194</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,21 +10237,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547607</v>
+        <v>547670</v>
       </c>
       <c r="R91" t="n">
-        <v>6960041</v>
+        <v>6960031</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10333,10 +10333,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128279069</v>
+        <v>128279287</v>
       </c>
       <c r="B92" t="n">
-        <v>80194</v>
+        <v>91763</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10344,21 +10344,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>547670</v>
+        <v>547607</v>
       </c>
       <c r="R92" t="n">
-        <v>6960031</v>
+        <v>6960041</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10884,7 +10884,7 @@
         <v>128622886</v>
       </c>
       <c r="B97" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>128622883</v>
       </c>
       <c r="B98" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6032,7 +6032,7 @@
         <v>128278178</v>
       </c>
       <c r="B52" t="n">
-        <v>92041</v>
+        <v>92068</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>128279532</v>
       </c>
       <c r="B53" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6243,48 +6243,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128284865</v>
+        <v>128278898</v>
       </c>
       <c r="B54" t="n">
-        <v>98613</v>
+        <v>80221</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547591</v>
+        <v>547758</v>
       </c>
       <c r="R54" t="n">
-        <v>6960277</v>
+        <v>6960041</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6338,60 +6338,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128278898</v>
+        <v>128284865</v>
       </c>
       <c r="B55" t="n">
-        <v>80194</v>
+        <v>98640</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547758</v>
+        <v>547591</v>
       </c>
       <c r="R55" t="n">
-        <v>6960041</v>
+        <v>6960277</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6445,22 +6445,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128278960</v>
+        <v>128278869</v>
       </c>
       <c r="B56" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6487,7 +6487,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6496,10 +6501,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547724</v>
+        <v>547767</v>
       </c>
       <c r="R56" t="n">
-        <v>6960039</v>
+        <v>6960048</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6536,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6541,7 +6546,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6556,22 +6561,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128278869</v>
+        <v>128278960</v>
       </c>
       <c r="B57" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6598,12 +6603,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547767</v>
+        <v>547724</v>
       </c>
       <c r="R57" t="n">
-        <v>6960048</v>
+        <v>6960039</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,66 +6672,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128279511</v>
+        <v>128279150</v>
       </c>
       <c r="B58" t="n">
-        <v>98592</v>
+        <v>92776</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547618</v>
+        <v>547640</v>
       </c>
       <c r="R58" t="n">
-        <v>6960012</v>
+        <v>6960059</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6763,7 +6754,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6773,7 +6764,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6788,57 +6779,66 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128279150</v>
+        <v>128279511</v>
       </c>
       <c r="B59" t="n">
-        <v>92749</v>
+        <v>98619</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547640</v>
+        <v>547618</v>
       </c>
       <c r="R59" t="n">
-        <v>6960059</v>
+        <v>6960012</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6895,12 +6895,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6910,7 +6910,7 @@
         <v>128277912</v>
       </c>
       <c r="B60" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>128284869</v>
       </c>
       <c r="B61" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>128279022</v>
       </c>
       <c r="B62" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>128284859</v>
       </c>
       <c r="B63" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7325,10 +7325,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B64" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R64" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,10 +7432,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B65" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R65" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7542,7 +7542,7 @@
         <v>128279803</v>
       </c>
       <c r="B66" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7636,10 +7636,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B67" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7676,10 +7676,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R67" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128280133</v>
+        <v>128280081</v>
       </c>
       <c r="B68" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547601</v>
+        <v>547586</v>
       </c>
       <c r="R68" t="n">
-        <v>6960267</v>
+        <v>6960259</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7853,7 +7853,7 @@
         <v>128284861</v>
       </c>
       <c r="B69" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>128278944</v>
       </c>
       <c r="B70" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8068,48 +8068,52 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128284870</v>
+        <v>128279241</v>
       </c>
       <c r="B71" t="n">
-        <v>92164</v>
+        <v>98619</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547621</v>
+        <v>547618</v>
       </c>
       <c r="R71" t="n">
-        <v>6960289</v>
+        <v>6960049</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8138,7 +8142,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8148,7 +8152,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,22 +8167,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128279241</v>
+        <v>128279186</v>
       </c>
       <c r="B72" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8210,14 +8214,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547618</v>
+        <v>547558</v>
       </c>
       <c r="R72" t="n">
-        <v>6960049</v>
+        <v>6960050</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8247,19 +8251,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8274,61 +8268,62 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128279186</v>
+        <v>128278487</v>
       </c>
       <c r="B73" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>547558</v>
+        <v>547771</v>
       </c>
       <c r="R73" t="n">
-        <v>6960050</v>
+        <v>6960077</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,6 +8356,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8387,53 +8387,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128278487</v>
+        <v>128284870</v>
       </c>
       <c r="B74" t="n">
-        <v>57689</v>
+        <v>92191</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>547771</v>
+        <v>547621</v>
       </c>
       <c r="R74" t="n">
-        <v>6960077</v>
+        <v>6960289</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8460,14 +8455,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8482,64 +8482,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B75" t="n">
-        <v>98592</v>
+        <v>57876</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R75" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8568,7 +8564,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8578,7 +8574,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8593,60 +8594,64 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B76" t="n">
-        <v>57849</v>
+        <v>98619</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R76" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8675,7 +8680,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8685,12 +8690,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,60 +8705,64 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128284860</v>
+        <v>128278726</v>
       </c>
       <c r="B77" t="n">
-        <v>92775</v>
+        <v>98619</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547847</v>
+        <v>547806</v>
       </c>
       <c r="R77" t="n">
-        <v>6960134</v>
+        <v>6960028</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8787,7 +8791,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8797,7 +8801,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,22 +8816,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128278595</v>
+        <v>128284860</v>
       </c>
       <c r="B78" t="n">
-        <v>80194</v>
+        <v>92802</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8835,37 +8839,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>4368</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547811</v>
+        <v>547847</v>
       </c>
       <c r="R78" t="n">
-        <v>6960055</v>
+        <v>6960134</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8894,7 +8898,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8904,7 +8908,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8919,61 +8923,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278726</v>
+        <v>128278595</v>
       </c>
       <c r="B79" t="n">
-        <v>98592</v>
+        <v>80221</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547806</v>
+        <v>547811</v>
       </c>
       <c r="R79" t="n">
-        <v>6960028</v>
+        <v>6960055</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,12 +9030,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9045,7 +9045,7 @@
         <v>128277499</v>
       </c>
       <c r="B80" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>128284867</v>
       </c>
       <c r="B81" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>128284866</v>
       </c>
       <c r="B82" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>128280541</v>
       </c>
       <c r="B83" t="n">
-        <v>92041</v>
+        <v>92068</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>128279138</v>
       </c>
       <c r="B84" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>128277635</v>
       </c>
       <c r="B85" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>128277916</v>
       </c>
       <c r="B86" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9791,10 +9791,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128278910</v>
+        <v>128279883</v>
       </c>
       <c r="B87" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9821,19 +9821,19 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>547750</v>
+        <v>547596</v>
       </c>
       <c r="R87" t="n">
-        <v>6960045</v>
+        <v>6960103</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9863,19 +9863,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9890,22 +9880,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128278608</v>
+        <v>128278910</v>
       </c>
       <c r="B88" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9932,7 +9922,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9941,10 +9931,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>547814</v>
+        <v>547750</v>
       </c>
       <c r="R88" t="n">
-        <v>6960059</v>
+        <v>6960045</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9976,7 +9966,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9986,7 +9976,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10013,10 +10003,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128279883</v>
+        <v>128278608</v>
       </c>
       <c r="B89" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10043,19 +10033,19 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>547596</v>
+        <v>547814</v>
       </c>
       <c r="R89" t="n">
-        <v>6960103</v>
+        <v>6960059</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10085,9 +10075,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10102,12 +10102,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10117,7 +10117,7 @@
         <v>128284862</v>
       </c>
       <c r="B90" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10226,10 +10226,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128279069</v>
+        <v>128279287</v>
       </c>
       <c r="B91" t="n">
-        <v>80194</v>
+        <v>91790</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,21 +10237,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547670</v>
+        <v>547607</v>
       </c>
       <c r="R91" t="n">
-        <v>6960031</v>
+        <v>6960041</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10333,10 +10333,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128279287</v>
+        <v>128284863</v>
       </c>
       <c r="B92" t="n">
-        <v>91763</v>
+        <v>56898</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10344,37 +10344,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>547607</v>
+        <v>547756</v>
       </c>
       <c r="R92" t="n">
-        <v>6960041</v>
+        <v>6960112</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10428,22 +10428,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128284863</v>
+        <v>128279069</v>
       </c>
       <c r="B93" t="n">
-        <v>56871</v>
+        <v>80221</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,37 +10451,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547756</v>
+        <v>547670</v>
       </c>
       <c r="R93" t="n">
-        <v>6960112</v>
+        <v>6960031</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,12 +10535,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
         <v>128279518</v>
       </c>
       <c r="B94" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>128280491</v>
       </c>
       <c r="B95" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>128278124</v>
       </c>
       <c r="B96" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6350,48 +6350,57 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128284865</v>
+        <v>128278869</v>
       </c>
       <c r="B55" t="n">
-        <v>98640</v>
+        <v>98619</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547591</v>
+        <v>547767</v>
       </c>
       <c r="R55" t="n">
-        <v>6960277</v>
+        <v>6960048</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6420,7 +6429,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6430,7 +6439,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6445,69 +6454,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128278869</v>
+        <v>128284865</v>
       </c>
       <c r="B56" t="n">
-        <v>98619</v>
+        <v>98640</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547767</v>
+        <v>547591</v>
       </c>
       <c r="R56" t="n">
-        <v>6960048</v>
+        <v>6960277</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6561,12 +6561,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B64" t="n">
         <v>98619</v>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R64" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,7 +7432,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B65" t="n">
         <v>98619</v>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R65" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7636,7 +7636,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128280133</v>
+        <v>128280081</v>
       </c>
       <c r="B67" t="n">
         <v>57716</v>
@@ -7676,10 +7676,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547601</v>
+        <v>547586</v>
       </c>
       <c r="R67" t="n">
-        <v>6960267</v>
+        <v>6960259</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7743,7 +7743,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B68" t="n">
         <v>57716</v>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R68" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7850,48 +7850,52 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128284861</v>
+        <v>128278944</v>
       </c>
       <c r="B69" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547812</v>
+        <v>547605</v>
       </c>
       <c r="R69" t="n">
-        <v>6960137</v>
+        <v>6960074</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7920,7 +7924,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7930,7 +7934,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7945,64 +7949,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128278944</v>
+        <v>128284861</v>
       </c>
       <c r="B70" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547605</v>
+        <v>547812</v>
       </c>
       <c r="R70" t="n">
-        <v>6960074</v>
+        <v>6960137</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8056,64 +8056,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128279241</v>
+        <v>128284870</v>
       </c>
       <c r="B71" t="n">
-        <v>98619</v>
+        <v>92191</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547618</v>
+        <v>547621</v>
       </c>
       <c r="R71" t="n">
-        <v>6960049</v>
+        <v>6960289</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8142,7 +8138,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8152,7 +8148,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8167,61 +8163,62 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128279186</v>
+        <v>128278487</v>
       </c>
       <c r="B72" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547558</v>
+        <v>547771</v>
       </c>
       <c r="R72" t="n">
-        <v>6960050</v>
+        <v>6960077</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8254,6 +8251,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8280,50 +8282,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128278487</v>
+        <v>128279241</v>
       </c>
       <c r="B73" t="n">
-        <v>57716</v>
+        <v>98619</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>547771</v>
+        <v>547618</v>
       </c>
       <c r="R73" t="n">
-        <v>6960077</v>
+        <v>6960049</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8353,14 +8354,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8375,60 +8381,64 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128284870</v>
+        <v>128279186</v>
       </c>
       <c r="B74" t="n">
-        <v>92191</v>
+        <v>98619</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>547621</v>
+        <v>547558</v>
       </c>
       <c r="R74" t="n">
-        <v>6960289</v>
+        <v>6960050</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8455,19 +8465,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8482,60 +8482,64 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B75" t="n">
-        <v>57876</v>
+        <v>98619</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R75" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8564,7 +8568,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8574,12 +8578,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8594,64 +8593,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B76" t="n">
-        <v>98619</v>
+        <v>57876</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R76" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8680,7 +8675,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8690,7 +8685,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,61 +8705,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128278726</v>
+        <v>128278595</v>
       </c>
       <c r="B77" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547806</v>
+        <v>547811</v>
       </c>
       <c r="R77" t="n">
-        <v>6960028</v>
+        <v>6960055</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8791,7 +8787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8801,7 +8797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,12 +8812,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8935,45 +8931,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128278595</v>
+        <v>128278726</v>
       </c>
       <c r="B79" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>547811</v>
+        <v>547806</v>
       </c>
       <c r="R79" t="n">
-        <v>6960055</v>
+        <v>6960028</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,12 +9030,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9149,32 +9149,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128284867</v>
+        <v>128284866</v>
       </c>
       <c r="B81" t="n">
-        <v>80250</v>
+        <v>80221</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9187,10 +9187,10 @@
         <v>547611</v>
       </c>
       <c r="R81" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9256,32 +9256,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128284866</v>
+        <v>128280541</v>
       </c>
       <c r="B82" t="n">
-        <v>80221</v>
+        <v>92068</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R82" t="n">
-        <v>6960291</v>
+        <v>6960341</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9324,19 +9324,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,44 +9341,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128280541</v>
+        <v>128284867</v>
       </c>
       <c r="B83" t="n">
-        <v>92068</v>
+        <v>80250</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9398,13 +9388,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R83" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9431,9 +9421,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9448,12 +9448,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9791,52 +9791,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128279883</v>
+        <v>128284862</v>
       </c>
       <c r="B87" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>547596</v>
+        <v>547776</v>
       </c>
       <c r="R87" t="n">
-        <v>6960103</v>
+        <v>6960134</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9863,9 +9859,24 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9880,12 +9891,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10114,48 +10125,52 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128284862</v>
+        <v>128279883</v>
       </c>
       <c r="B90" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>547776</v>
+        <v>547596</v>
       </c>
       <c r="R90" t="n">
-        <v>6960134</v>
+        <v>6960103</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10182,24 +10197,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10214,12 +10214,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10333,10 +10333,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128284863</v>
+        <v>128279069</v>
       </c>
       <c r="B92" t="n">
-        <v>56898</v>
+        <v>80221</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10344,37 +10344,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>547756</v>
+        <v>547670</v>
       </c>
       <c r="R92" t="n">
-        <v>6960112</v>
+        <v>6960031</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10428,22 +10428,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128279069</v>
+        <v>128284863</v>
       </c>
       <c r="B93" t="n">
-        <v>80221</v>
+        <v>56898</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,37 +10451,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547670</v>
+        <v>547756</v>
       </c>
       <c r="R93" t="n">
-        <v>6960031</v>
+        <v>6960112</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,12 +10535,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10884,7 +10884,7 @@
         <v>128622886</v>
       </c>
       <c r="B97" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>128622883</v>
       </c>
       <c r="B98" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6032,7 +6032,7 @@
         <v>128278178</v>
       </c>
       <c r="B52" t="n">
-        <v>92068</v>
+        <v>92078</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6126,50 +6126,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128279532</v>
+        <v>128278960</v>
       </c>
       <c r="B53" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547624</v>
+        <v>547724</v>
       </c>
       <c r="R53" t="n">
-        <v>6960008</v>
+        <v>6960039</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6201,7 +6200,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6211,12 +6210,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6231,57 +6225,66 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128278898</v>
+        <v>128278869</v>
       </c>
       <c r="B54" t="n">
-        <v>80221</v>
+        <v>98632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547758</v>
+        <v>547767</v>
       </c>
       <c r="R54" t="n">
-        <v>6960041</v>
+        <v>6960048</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6313,7 +6316,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6323,7 +6326,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6350,57 +6353,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128278869</v>
+        <v>128284865</v>
       </c>
       <c r="B55" t="n">
-        <v>98619</v>
+        <v>98653</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547767</v>
+        <v>547591</v>
       </c>
       <c r="R55" t="n">
-        <v>6960048</v>
+        <v>6960277</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6429,7 +6423,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6439,7 +6433,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6454,60 +6448,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128284865</v>
+        <v>128278898</v>
       </c>
       <c r="B56" t="n">
-        <v>98640</v>
+        <v>80225</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547591</v>
+        <v>547758</v>
       </c>
       <c r="R56" t="n">
-        <v>6960277</v>
+        <v>6960041</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6536,7 +6530,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6546,7 +6540,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6561,61 +6555,62 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128278960</v>
+        <v>128279532</v>
       </c>
       <c r="B57" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547724</v>
+        <v>547624</v>
       </c>
       <c r="R57" t="n">
-        <v>6960039</v>
+        <v>6960008</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6647,7 +6642,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6657,7 +6652,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,12 +6672,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
         <v>128279150</v>
       </c>
       <c r="B58" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>128279511</v>
       </c>
       <c r="B59" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>128277912</v>
       </c>
       <c r="B60" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>128284869</v>
       </c>
       <c r="B61" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>128279022</v>
       </c>
       <c r="B62" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>128284859</v>
       </c>
       <c r="B63" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>128284872</v>
       </c>
       <c r="B64" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>128284868</v>
       </c>
       <c r="B65" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128279803</v>
+        <v>128280081</v>
       </c>
       <c r="B66" t="n">
-        <v>92778</v>
+        <v>57716</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7550,34 +7550,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547600</v>
+        <v>547586</v>
       </c>
       <c r="R66" t="n">
-        <v>6960084</v>
+        <v>6960259</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7610,6 +7615,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7636,7 +7646,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B67" t="n">
         <v>57716</v>
@@ -7676,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R67" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7743,10 +7753,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128280133</v>
+        <v>128279803</v>
       </c>
       <c r="B68" t="n">
-        <v>57716</v>
+        <v>92788</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7754,39 +7764,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547601</v>
+        <v>547600</v>
       </c>
       <c r="R68" t="n">
-        <v>6960267</v>
+        <v>6960084</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7819,11 +7824,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7850,52 +7850,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128278944</v>
+        <v>128284861</v>
       </c>
       <c r="B69" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547605</v>
+        <v>547812</v>
       </c>
       <c r="R69" t="n">
-        <v>6960074</v>
+        <v>6960137</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7924,7 +7920,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7934,7 +7930,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7949,60 +7945,64 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128284861</v>
+        <v>128278944</v>
       </c>
       <c r="B70" t="n">
-        <v>80221</v>
+        <v>98632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547812</v>
+        <v>547605</v>
       </c>
       <c r="R70" t="n">
-        <v>6960137</v>
+        <v>6960074</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8056,60 +8056,64 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128284870</v>
+        <v>128279241</v>
       </c>
       <c r="B71" t="n">
-        <v>92191</v>
+        <v>98632</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547621</v>
+        <v>547618</v>
       </c>
       <c r="R71" t="n">
-        <v>6960289</v>
+        <v>6960049</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8138,7 +8142,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8148,7 +8152,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,62 +8167,61 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128278487</v>
+        <v>128279186</v>
       </c>
       <c r="B72" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547771</v>
+        <v>547558</v>
       </c>
       <c r="R72" t="n">
-        <v>6960077</v>
+        <v>6960050</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8251,11 +8254,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8282,52 +8280,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128279241</v>
+        <v>128284870</v>
       </c>
       <c r="B73" t="n">
-        <v>98619</v>
+        <v>92201</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>547618</v>
+        <v>547621</v>
       </c>
       <c r="R73" t="n">
-        <v>6960049</v>
+        <v>6960289</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8356,7 +8350,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8366,7 +8360,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8381,61 +8375,62 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128279186</v>
+        <v>128278487</v>
       </c>
       <c r="B74" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>547558</v>
+        <v>547771</v>
       </c>
       <c r="R74" t="n">
-        <v>6960050</v>
+        <v>6960077</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8468,6 +8463,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8497,7 +8497,7 @@
         <v>128278988</v>
       </c>
       <c r="B75" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>128278595</v>
       </c>
       <c r="B77" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>128284860</v>
       </c>
       <c r="B78" t="n">
-        <v>92802</v>
+        <v>92812</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>128278726</v>
       </c>
       <c r="B79" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9042,10 +9042,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128277499</v>
+        <v>128284866</v>
       </c>
       <c r="B80" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9073,14 +9073,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>547884</v>
+        <v>547611</v>
       </c>
       <c r="R80" t="n">
-        <v>6960163</v>
+        <v>6960291</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9137,22 +9137,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128284866</v>
+        <v>128277499</v>
       </c>
       <c r="B81" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9180,14 +9180,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>547611</v>
+        <v>547884</v>
       </c>
       <c r="R81" t="n">
-        <v>6960291</v>
+        <v>6960163</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9244,44 +9244,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128280541</v>
+        <v>128284867</v>
       </c>
       <c r="B82" t="n">
-        <v>92068</v>
+        <v>80254</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9291,13 +9291,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R82" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9324,9 +9324,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9341,44 +9351,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128284867</v>
+        <v>128280541</v>
       </c>
       <c r="B83" t="n">
-        <v>80250</v>
+        <v>92078</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9388,13 +9398,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R83" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9421,19 +9431,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9448,62 +9448,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128279138</v>
+        <v>128277635</v>
       </c>
       <c r="B84" t="n">
-        <v>57716</v>
+        <v>92794</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>547548</v>
+        <v>547856</v>
       </c>
       <c r="R84" t="n">
-        <v>6960061</v>
+        <v>6960149</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9533,14 +9528,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9555,57 +9555,62 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128277635</v>
+        <v>128279138</v>
       </c>
       <c r="B85" t="n">
-        <v>92784</v>
+        <v>57716</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>547856</v>
+        <v>547548</v>
       </c>
       <c r="R85" t="n">
-        <v>6960149</v>
+        <v>6960061</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,19 +9640,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9662,12 +9662,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9791,48 +9791,52 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128284862</v>
+        <v>128278910</v>
       </c>
       <c r="B87" t="n">
-        <v>80221</v>
+        <v>98632</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>547776</v>
+        <v>547750</v>
       </c>
       <c r="R87" t="n">
-        <v>6960134</v>
+        <v>6960045</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9861,7 +9865,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9871,12 +9875,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9891,22 +9890,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128278910</v>
+        <v>128278608</v>
       </c>
       <c r="B88" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9933,7 +9932,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9942,10 +9941,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>547750</v>
+        <v>547814</v>
       </c>
       <c r="R88" t="n">
-        <v>6960045</v>
+        <v>6960059</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9977,7 +9976,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9987,7 +9986,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10014,10 +10013,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128278608</v>
+        <v>128279883</v>
       </c>
       <c r="B89" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10044,19 +10043,19 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>547814</v>
+        <v>547596</v>
       </c>
       <c r="R89" t="n">
-        <v>6960059</v>
+        <v>6960103</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10086,19 +10085,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10113,64 +10102,60 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128279883</v>
+        <v>128284862</v>
       </c>
       <c r="B90" t="n">
-        <v>98619</v>
+        <v>80225</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>547596</v>
+        <v>547776</v>
       </c>
       <c r="R90" t="n">
-        <v>6960103</v>
+        <v>6960134</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10197,9 +10182,24 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10214,22 +10214,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128279287</v>
+        <v>128279069</v>
       </c>
       <c r="B91" t="n">
-        <v>91790</v>
+        <v>80225</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10237,21 +10237,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>547607</v>
+        <v>547670</v>
       </c>
       <c r="R91" t="n">
-        <v>6960041</v>
+        <v>6960031</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10333,10 +10333,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128279069</v>
+        <v>128284863</v>
       </c>
       <c r="B92" t="n">
-        <v>80221</v>
+        <v>56898</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10344,37 +10344,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>547670</v>
+        <v>547756</v>
       </c>
       <c r="R92" t="n">
-        <v>6960031</v>
+        <v>6960112</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10428,22 +10428,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128284863</v>
+        <v>128279287</v>
       </c>
       <c r="B93" t="n">
-        <v>56898</v>
+        <v>91800</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,37 +10451,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>547756</v>
+        <v>547607</v>
       </c>
       <c r="R93" t="n">
-        <v>6960112</v>
+        <v>6960041</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10535,12 +10535,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
         <v>128279518</v>
       </c>
       <c r="B94" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>128278124</v>
       </c>
       <c r="B96" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -6126,49 +6126,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128278960</v>
+        <v>128278898</v>
       </c>
       <c r="B53" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547724</v>
+        <v>547758</v>
       </c>
       <c r="R53" t="n">
-        <v>6960039</v>
+        <v>6960041</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6200,7 +6196,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6210,7 +6206,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6225,69 +6221,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128278869</v>
+        <v>128284865</v>
       </c>
       <c r="B54" t="n">
-        <v>98632</v>
+        <v>98653</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547767</v>
+        <v>547591</v>
       </c>
       <c r="R54" t="n">
-        <v>6960048</v>
+        <v>6960277</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6316,7 +6303,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6326,7 +6313,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6341,60 +6328,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128284865</v>
+        <v>128279532</v>
       </c>
       <c r="B55" t="n">
-        <v>98653</v>
+        <v>57716</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547591</v>
+        <v>547624</v>
       </c>
       <c r="R55" t="n">
-        <v>6960277</v>
+        <v>6960008</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6423,7 +6415,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6433,7 +6425,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6448,57 +6445,66 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128278898</v>
+        <v>128278869</v>
       </c>
       <c r="B56" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547758</v>
+        <v>547767</v>
       </c>
       <c r="R56" t="n">
-        <v>6960041</v>
+        <v>6960048</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6530,7 +6536,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6540,7 +6546,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6567,50 +6573,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128279532</v>
+        <v>128278960</v>
       </c>
       <c r="B57" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547624</v>
+        <v>547724</v>
       </c>
       <c r="R57" t="n">
-        <v>6960008</v>
+        <v>6960039</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6642,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6652,12 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,12 +6672,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B64" t="n">
         <v>98632</v>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R64" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,7 +7432,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B65" t="n">
         <v>98632</v>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R65" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7539,10 +7539,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128280081</v>
+        <v>128279803</v>
       </c>
       <c r="B66" t="n">
-        <v>57716</v>
+        <v>92788</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7550,39 +7550,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547586</v>
+        <v>547600</v>
       </c>
       <c r="R66" t="n">
-        <v>6960259</v>
+        <v>6960084</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7615,11 +7610,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7646,7 +7636,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128280133</v>
+        <v>128280081</v>
       </c>
       <c r="B67" t="n">
         <v>57716</v>
@@ -7686,10 +7676,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547601</v>
+        <v>547586</v>
       </c>
       <c r="R67" t="n">
-        <v>6960267</v>
+        <v>6960259</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7753,10 +7743,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128279803</v>
+        <v>128280133</v>
       </c>
       <c r="B68" t="n">
-        <v>92788</v>
+        <v>57716</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7764,34 +7754,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547600</v>
+        <v>547601</v>
       </c>
       <c r="R68" t="n">
-        <v>6960084</v>
+        <v>6960267</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7824,6 +7819,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8068,52 +8068,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128279241</v>
+        <v>128284870</v>
       </c>
       <c r="B71" t="n">
-        <v>98632</v>
+        <v>92201</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>547618</v>
+        <v>547621</v>
       </c>
       <c r="R71" t="n">
-        <v>6960049</v>
+        <v>6960289</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8142,7 +8138,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8152,7 +8148,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8167,61 +8163,62 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128279186</v>
+        <v>128278487</v>
       </c>
       <c r="B72" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>547558</v>
+        <v>547771</v>
       </c>
       <c r="R72" t="n">
-        <v>6960050</v>
+        <v>6960077</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8254,6 +8251,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8280,48 +8282,52 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128284870</v>
+        <v>128279241</v>
       </c>
       <c r="B73" t="n">
-        <v>92201</v>
+        <v>98632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>547621</v>
+        <v>547618</v>
       </c>
       <c r="R73" t="n">
-        <v>6960289</v>
+        <v>6960049</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8350,7 +8356,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8360,7 +8366,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8375,62 +8381,61 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128278487</v>
+        <v>128279186</v>
       </c>
       <c r="B74" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>547771</v>
+        <v>547558</v>
       </c>
       <c r="R74" t="n">
-        <v>6960077</v>
+        <v>6960050</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8463,11 +8468,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8494,52 +8494,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128278988</v>
+        <v>128284864</v>
       </c>
       <c r="B75" t="n">
-        <v>98632</v>
+        <v>57876</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>547739</v>
+        <v>547576</v>
       </c>
       <c r="R75" t="n">
-        <v>6960028</v>
+        <v>6960160</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8568,7 +8564,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8578,7 +8574,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>par</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8593,60 +8594,64 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128284864</v>
+        <v>128278988</v>
       </c>
       <c r="B76" t="n">
-        <v>57876</v>
+        <v>98632</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>547576</v>
+        <v>547739</v>
       </c>
       <c r="R76" t="n">
-        <v>6960160</v>
+        <v>6960028</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8675,7 +8680,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8685,12 +8690,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>par</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,22 +8705,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128278595</v>
+        <v>128284860</v>
       </c>
       <c r="B77" t="n">
-        <v>80225</v>
+        <v>92812</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8728,37 +8728,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>4368</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>547811</v>
+        <v>547847</v>
       </c>
       <c r="R77" t="n">
-        <v>6960055</v>
+        <v>6960134</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,22 +8812,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128284860</v>
+        <v>128278595</v>
       </c>
       <c r="B78" t="n">
-        <v>92812</v>
+        <v>80225</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8835,37 +8835,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4368</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>547847</v>
+        <v>547811</v>
       </c>
       <c r="R78" t="n">
-        <v>6960134</v>
+        <v>6960055</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8919,12 +8919,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9042,32 +9042,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128284866</v>
+        <v>128280541</v>
       </c>
       <c r="B80" t="n">
-        <v>80225</v>
+        <v>92078</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R80" t="n">
-        <v>6960291</v>
+        <v>6960341</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9110,19 +9110,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9137,12 +9127,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9363,32 +9353,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128280541</v>
+        <v>128284866</v>
       </c>
       <c r="B83" t="n">
-        <v>92078</v>
+        <v>80225</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9398,10 +9388,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R83" t="n">
-        <v>6960341</v>
+        <v>6960291</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9431,9 +9421,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9448,57 +9448,62 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128277635</v>
+        <v>128279138</v>
       </c>
       <c r="B84" t="n">
-        <v>92794</v>
+        <v>57716</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>547856</v>
+        <v>547548</v>
       </c>
       <c r="R84" t="n">
-        <v>6960149</v>
+        <v>6960061</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,19 +9533,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9555,62 +9555,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128279138</v>
+        <v>128277635</v>
       </c>
       <c r="B85" t="n">
-        <v>57716</v>
+        <v>92794</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>547548</v>
+        <v>547856</v>
       </c>
       <c r="R85" t="n">
-        <v>6960061</v>
+        <v>6960149</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9640,14 +9635,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9662,12 +9662,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9791,52 +9791,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128278910</v>
+        <v>128284862</v>
       </c>
       <c r="B87" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>547750</v>
+        <v>547776</v>
       </c>
       <c r="R87" t="n">
-        <v>6960045</v>
+        <v>6960134</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9865,7 +9861,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9875,7 +9871,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9890,19 +9891,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128278608</v>
+        <v>128278910</v>
       </c>
       <c r="B88" t="n">
         <v>98632</v>
@@ -9932,7 +9933,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9941,10 +9942,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>547814</v>
+        <v>547750</v>
       </c>
       <c r="R88" t="n">
-        <v>6960059</v>
+        <v>6960045</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9976,7 +9977,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9986,7 +9987,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10013,7 +10014,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128279883</v>
+        <v>128278608</v>
       </c>
       <c r="B89" t="n">
         <v>98632</v>
@@ -10043,19 +10044,19 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>547596</v>
+        <v>547814</v>
       </c>
       <c r="R89" t="n">
-        <v>6960103</v>
+        <v>6960059</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10085,9 +10086,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10102,60 +10113,64 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128284862</v>
+        <v>128279883</v>
       </c>
       <c r="B90" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>547776</v>
+        <v>547596</v>
       </c>
       <c r="R90" t="n">
-        <v>6960134</v>
+        <v>6960103</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10182,24 +10197,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10214,12 +10214,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -7850,48 +7850,52 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128284861</v>
+        <v>128278944</v>
       </c>
       <c r="B69" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547812</v>
+        <v>547605</v>
       </c>
       <c r="R69" t="n">
-        <v>6960137</v>
+        <v>6960074</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7920,7 +7924,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7930,7 +7934,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7945,64 +7949,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128278944</v>
+        <v>128284861</v>
       </c>
       <c r="B70" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrkrången, Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547605</v>
+        <v>547812</v>
       </c>
       <c r="R70" t="n">
-        <v>6960074</v>
+        <v>6960137</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8056,12 +8056,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9460,50 +9460,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128279138</v>
+        <v>128277635</v>
       </c>
       <c r="B84" t="n">
-        <v>57716</v>
+        <v>92794</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrkrången, Jmt</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>547548</v>
+        <v>547856</v>
       </c>
       <c r="R84" t="n">
-        <v>6960061</v>
+        <v>6960149</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9533,14 +9528,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9555,57 +9555,62 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128277635</v>
+        <v>128279138</v>
       </c>
       <c r="B85" t="n">
-        <v>92794</v>
+        <v>57716</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Jmt</t>
+          <t>Norrkrången, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>547856</v>
+        <v>547548</v>
       </c>
       <c r="R85" t="n">
-        <v>6960149</v>
+        <v>6960061</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,19 +9640,14 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9662,12 +9662,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -10884,7 +10884,7 @@
         <v>128622886</v>
       </c>
       <c r="B97" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>128622883</v>
       </c>
       <c r="B98" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -10768,7 +10768,7 @@
         <v>128278124</v>
       </c>
       <c r="B96" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -10884,7 +10884,7 @@
         <v>128622886</v>
       </c>
       <c r="B97" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>128622883</v>
       </c>
       <c r="B98" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -10884,7 +10884,7 @@
         <v>128622886</v>
       </c>
       <c r="B97" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>128622883</v>
       </c>
       <c r="B98" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -10884,7 +10884,7 @@
         <v>128622886</v>
       </c>
       <c r="B97" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>128622883</v>
       </c>
       <c r="B98" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AY102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11073,6 +11073,454 @@
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129640430</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>547934</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6960071</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129640431</v>
+      </c>
+      <c r="B100" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>548105</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6960118</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129640415</v>
+      </c>
+      <c r="B101" t="n">
+        <v>96973</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>53</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>548058</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6960043</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129640429</v>
+      </c>
+      <c r="B102" t="n">
+        <v>92331</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>547918</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6960064</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -11078,7 +11078,7 @@
         <v>129640430</v>
       </c>
       <c r="B99" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>129640431</v>
       </c>
       <c r="B100" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>129640415</v>
       </c>
       <c r="B101" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>129640429</v>
       </c>
       <c r="B102" t="n">
-        <v>92331</v>
+        <v>92359</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -11078,7 +11078,7 @@
         <v>129640430</v>
       </c>
       <c r="B99" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>129640431</v>
       </c>
       <c r="B100" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>129640415</v>
       </c>
       <c r="B101" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>129640429</v>
       </c>
       <c r="B102" t="n">
-        <v>92359</v>
+        <v>92365</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -11078,7 +11078,7 @@
         <v>129640430</v>
       </c>
       <c r="B99" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>129640431</v>
       </c>
       <c r="B100" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>129640415</v>
       </c>
       <c r="B101" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>129640429</v>
       </c>
       <c r="B102" t="n">
-        <v>92365</v>
+        <v>92366</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -11078,7 +11078,7 @@
         <v>129640430</v>
       </c>
       <c r="B99" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>129640431</v>
       </c>
       <c r="B100" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>129640415</v>
       </c>
       <c r="B101" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>129640429</v>
       </c>
       <c r="B102" t="n">
-        <v>92366</v>
+        <v>92371</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -11078,7 +11078,7 @@
         <v>129640430</v>
       </c>
       <c r="B99" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>129640431</v>
       </c>
       <c r="B100" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>129640415</v>
       </c>
       <c r="B101" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>129640429</v>
       </c>
       <c r="B102" t="n">
-        <v>92371</v>
+        <v>92375</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -11078,7 +11078,7 @@
         <v>129640430</v>
       </c>
       <c r="B99" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>129640431</v>
       </c>
       <c r="B100" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>129640415</v>
       </c>
       <c r="B101" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>129640429</v>
       </c>
       <c r="B102" t="n">
-        <v>92375</v>
+        <v>92377</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -11078,7 +11078,7 @@
         <v>129640430</v>
       </c>
       <c r="B99" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>129640431</v>
       </c>
       <c r="B100" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>129640415</v>
       </c>
       <c r="B101" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -11078,7 +11078,7 @@
         <v>129640430</v>
       </c>
       <c r="B99" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>129640431</v>
       </c>
       <c r="B100" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>129640415</v>
       </c>
       <c r="B101" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>129640429</v>
       </c>
       <c r="B102" t="n">
-        <v>92377</v>
+        <v>92380</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -11078,7 +11078,7 @@
         <v>129640430</v>
       </c>
       <c r="B99" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>129640431</v>
       </c>
       <c r="B100" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>129640415</v>
       </c>
       <c r="B101" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>129640429</v>
       </c>
       <c r="B102" t="n">
-        <v>92380</v>
+        <v>92383</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -11078,7 +11078,7 @@
         <v>129640430</v>
       </c>
       <c r="B99" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>129640431</v>
       </c>
       <c r="B100" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>129640415</v>
       </c>
       <c r="B101" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>129640429</v>
       </c>
       <c r="B102" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 46328-2022 artfynd.xlsx
+++ b/artfynd/A 46328-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY118"/>
+  <dimension ref="A1:AZ118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640414</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640415</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279287</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043849</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043850</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043851</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010397</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278178</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128280541</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1690,6 +1740,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128622890</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043803</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1902,6 +1962,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640429</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1999,6 +2064,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043813</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2096,6 +2166,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128277912</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2193,6 +2268,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128622883</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2300,6 +2380,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284870</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2492,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279150</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2504,6 +2594,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279803</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2611,6 +2706,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128277456</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2718,6 +2818,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128277635</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2815,6 +2920,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128622889</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2912,6 +3022,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043814</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3019,6 +3134,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284860</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3116,6 +3236,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043800</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3213,6 +3338,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043811</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3310,6 +3440,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043809</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3407,6 +3542,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043810</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3508,6 +3648,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043840</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3609,6 +3754,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043841</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3710,6 +3860,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043842</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3811,6 +3966,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043843</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3912,6 +4072,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043845</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4013,6 +4178,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043847</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4114,6 +4284,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043848</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4211,6 +4386,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043853</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4318,6 +4498,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284869</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4429,6 +4614,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640417</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4540,6 +4730,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640423</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4637,6 +4832,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043816</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4734,6 +4934,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043817</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4831,6 +5036,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043818</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4928,6 +5138,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043820</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5025,6 +5240,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043821</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5122,6 +5342,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043822</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5219,6 +5444,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043823</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5316,6 +5546,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043824</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5413,6 +5648,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043826</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5510,6 +5750,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043827</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5607,6 +5852,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043828</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5704,6 +5954,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043830</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5801,6 +6056,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043831</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5898,6 +6158,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043832</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5995,6 +6260,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043833</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6092,6 +6362,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043834</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6189,6 +6464,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043835</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6286,6 +6566,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043836</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6383,6 +6668,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043837</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6480,6 +6770,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043838</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6587,6 +6882,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128277499</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6694,6 +6994,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278595</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6801,6 +7106,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278898</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6908,6 +7218,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279022</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7015,6 +7330,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279069</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7122,6 +7442,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284861</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7234,6 +7559,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284862</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7341,6 +7671,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284866</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7438,6 +7773,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128622886</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7545,6 +7885,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284867</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7651,6 +7996,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043804</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7757,6 +8107,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043805</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7863,6 +8218,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043806</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7987,6 +8347,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010401</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8111,6 +8476,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010404</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8218,6 +8588,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128277319</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8335,6 +8710,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128277916</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8442,6 +8822,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278487</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8549,6 +8934,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279138</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8666,6 +9056,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279532</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8773,6 +9168,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128280081</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8880,6 +9280,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128280133</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8987,6 +9392,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128280491</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9100,6 +9510,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112043808</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9216,6 +9631,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009740</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9323,6 +9743,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284863</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9434,6 +9859,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009742</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9545,6 +9975,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010661</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9656,6 +10091,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010402</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9767,6 +10207,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009743</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9883,6 +10328,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009753</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10007,6 +10457,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010649</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10118,6 +10573,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010665</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10230,6 +10690,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284864</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10337,6 +10802,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128277379</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10448,6 +10918,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128277337</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10564,6 +11039,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278124</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10675,6 +11155,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278608</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10786,6 +11271,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278726</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10902,6 +11392,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278869</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11013,6 +11508,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278910</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11124,6 +11624,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278944</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11235,6 +11740,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278960</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11346,6 +11856,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278988</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11447,6 +11962,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279186</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11558,6 +12078,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279241</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11674,6 +12199,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279511</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11785,6 +12315,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279518</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11886,6 +12421,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279883</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11993,6 +12533,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284859</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12100,6 +12645,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284868</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12207,6 +12757,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284872</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12318,6 +12873,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640416</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12429,6 +12989,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640426</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12540,6 +13105,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640427</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12651,6 +13221,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640428</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12762,6 +13337,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640430</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12873,6 +13453,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640431</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12980,8 +13565,132 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128284865</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>